--- a/research/traditional_assets/database/data/ireland/ireland_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07600297733566436</v>
+        <v>0.07594734861399477</v>
       </c>
       <c r="C2">
-        <v>583.0714395595312</v>
+        <v>577.5164601000727</v>
       </c>
       <c r="D2">
-        <v>448.2714395595312</v>
+        <v>448.5264601000727</v>
       </c>
       <c r="E2">
-        <v>-279.5</v>
+        <v>-273.69</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="G2">
         <v>134.8</v>
@@ -1451,28 +1451,28 @@
         <v>104.225</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.292243</v>
       </c>
       <c r="N2">
-        <v>104.225</v>
+        <v>103.932757</v>
       </c>
       <c r="O2">
-        <v>13.028125</v>
+        <v>12.991594625</v>
       </c>
       <c r="P2">
-        <v>91.19687499999999</v>
+        <v>90.94116237499999</v>
       </c>
       <c r="Q2">
-        <v>105.596875</v>
+        <v>105.341162375</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07600297733566436</v>
+        <v>0.07626992284241896</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5939155098363081</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>356.6381401778656</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07594734861399477</v>
+        <v>0.07589171989232518</v>
       </c>
       <c r="C3">
-        <v>577.5164601000727</v>
+        <v>571.9617709669207</v>
       </c>
       <c r="D3">
-        <v>448.5264601000727</v>
+        <v>448.7817709669207</v>
       </c>
       <c r="E3">
-        <v>-273.69</v>
+        <v>-267.88</v>
       </c>
       <c r="F3">
-        <v>5.81</v>
+        <v>11.62</v>
       </c>
       <c r="G3">
         <v>134.8</v>
@@ -1533,28 +1533,28 @@
         <v>104.225</v>
       </c>
       <c r="M3">
-        <v>0.292243</v>
+        <v>0.5844860000000001</v>
       </c>
       <c r="N3">
-        <v>103.932757</v>
+        <v>103.640514</v>
       </c>
       <c r="O3">
-        <v>12.991594625</v>
+        <v>12.95506425</v>
       </c>
       <c r="P3">
-        <v>90.94116237499999</v>
+        <v>90.68544975</v>
       </c>
       <c r="Q3">
-        <v>105.341162375</v>
+        <v>105.08544975</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07626992284241896</v>
+        <v>0.07654231621665836</v>
       </c>
       <c r="T3">
-        <v>0.5939155098363081</v>
+        <v>0.5992249637057547</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>356.6381401778656</v>
+        <v>178.3190700889328</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07589171989232518</v>
+        <v>0.07583609117065561</v>
       </c>
       <c r="C4">
-        <v>571.9617709669207</v>
+        <v>566.4073726561373</v>
       </c>
       <c r="D4">
-        <v>448.7817709669207</v>
+        <v>449.0373726561373</v>
       </c>
       <c r="E4">
-        <v>-267.88</v>
+        <v>-262.07</v>
       </c>
       <c r="F4">
-        <v>11.62</v>
+        <v>17.43</v>
       </c>
       <c r="G4">
         <v>134.8</v>
@@ -1615,28 +1615,28 @@
         <v>104.225</v>
       </c>
       <c r="M4">
-        <v>0.5844860000000001</v>
+        <v>0.876729</v>
       </c>
       <c r="N4">
-        <v>103.640514</v>
+        <v>103.348271</v>
       </c>
       <c r="O4">
-        <v>12.95506425</v>
+        <v>12.918533875</v>
       </c>
       <c r="P4">
-        <v>90.68544975</v>
+        <v>90.429737125</v>
       </c>
       <c r="Q4">
-        <v>105.08544975</v>
+        <v>104.829737125</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07654231621665836</v>
+        <v>0.07682032594912949</v>
       </c>
       <c r="T4">
-        <v>0.5992249637057547</v>
+        <v>0.6046438908508601</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>178.3190700889328</v>
+        <v>118.8793800592886</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07583609117065561</v>
+        <v>0.07578046244898602</v>
       </c>
       <c r="C5">
-        <v>566.4073726561373</v>
+        <v>560.8532656649159</v>
       </c>
       <c r="D5">
-        <v>449.0373726561373</v>
+        <v>449.2932656649158</v>
       </c>
       <c r="E5">
-        <v>-262.07</v>
+        <v>-256.26</v>
       </c>
       <c r="F5">
-        <v>17.43</v>
+        <v>23.24</v>
       </c>
       <c r="G5">
         <v>134.8</v>
@@ -1697,28 +1697,28 @@
         <v>104.225</v>
       </c>
       <c r="M5">
-        <v>0.876729</v>
+        <v>1.168972</v>
       </c>
       <c r="N5">
-        <v>103.348271</v>
+        <v>103.056028</v>
       </c>
       <c r="O5">
-        <v>12.918533875</v>
+        <v>12.8820035</v>
       </c>
       <c r="P5">
-        <v>90.429737125</v>
+        <v>90.1740245</v>
       </c>
       <c r="Q5">
-        <v>104.829737125</v>
+        <v>104.5740245</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07682032594912949</v>
+        <v>0.07710412755102711</v>
       </c>
       <c r="T5">
-        <v>0.6046438908508601</v>
+        <v>0.6101757123114886</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>118.8793800592886</v>
+        <v>89.15953504446641</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07578046244898602</v>
+        <v>0.07572483372731643</v>
       </c>
       <c r="C6">
-        <v>560.8532656649159</v>
+        <v>555.299450491583</v>
       </c>
       <c r="D6">
-        <v>449.2932656649158</v>
+        <v>449.549450491583</v>
       </c>
       <c r="E6">
-        <v>-256.26</v>
+        <v>-250.45</v>
       </c>
       <c r="F6">
-        <v>23.24</v>
+        <v>29.05</v>
       </c>
       <c r="G6">
         <v>134.8</v>
@@ -1779,28 +1779,28 @@
         <v>104.225</v>
       </c>
       <c r="M6">
-        <v>1.168972</v>
+        <v>1.461215</v>
       </c>
       <c r="N6">
-        <v>103.056028</v>
+        <v>102.763785</v>
       </c>
       <c r="O6">
-        <v>12.8820035</v>
+        <v>12.845473125</v>
       </c>
       <c r="P6">
-        <v>90.1740245</v>
+        <v>89.918311875</v>
       </c>
       <c r="Q6">
-        <v>104.5740245</v>
+        <v>104.318311875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07710412755102711</v>
+        <v>0.07739390392349099</v>
       </c>
       <c r="T6">
-        <v>0.6101757123114886</v>
+        <v>0.6158239931712882</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>89.15953504446641</v>
+        <v>71.32762803557314</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07572483372731643</v>
+        <v>0.07566920500564686</v>
       </c>
       <c r="C7">
-        <v>555.299450491583</v>
+        <v>549.7459276356032</v>
       </c>
       <c r="D7">
-        <v>449.549450491583</v>
+        <v>449.8059276356031</v>
       </c>
       <c r="E7">
-        <v>-250.45</v>
+        <v>-244.64</v>
       </c>
       <c r="F7">
-        <v>29.05</v>
+        <v>34.86</v>
       </c>
       <c r="G7">
         <v>134.8</v>
@@ -1861,28 +1861,28 @@
         <v>104.225</v>
       </c>
       <c r="M7">
-        <v>1.461215</v>
+        <v>1.753458</v>
       </c>
       <c r="N7">
-        <v>102.763785</v>
+        <v>102.471542</v>
       </c>
       <c r="O7">
-        <v>12.845473125</v>
+        <v>12.80894275</v>
       </c>
       <c r="P7">
-        <v>89.918311875</v>
+        <v>89.66259925</v>
       </c>
       <c r="Q7">
-        <v>104.318311875</v>
+        <v>104.06259925</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07739390392349099</v>
+        <v>0.07768984575068816</v>
       </c>
       <c r="T7">
-        <v>0.6158239931712882</v>
+        <v>0.6215924502195942</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>71.32762803557314</v>
+        <v>59.43969002964428</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07566920500564686</v>
+        <v>0.07561357628397729</v>
       </c>
       <c r="C8">
-        <v>549.7459276356032</v>
+        <v>544.1926975975806</v>
       </c>
       <c r="D8">
-        <v>449.8059276356031</v>
+        <v>450.0626975975806</v>
       </c>
       <c r="E8">
-        <v>-244.64</v>
+        <v>-238.83</v>
       </c>
       <c r="F8">
-        <v>34.86</v>
+        <v>40.66999999999999</v>
       </c>
       <c r="G8">
         <v>134.8</v>
@@ -1943,28 +1943,28 @@
         <v>104.225</v>
       </c>
       <c r="M8">
-        <v>1.753458</v>
+        <v>2.045701</v>
       </c>
       <c r="N8">
-        <v>102.471542</v>
+        <v>102.179299</v>
       </c>
       <c r="O8">
-        <v>12.80894275</v>
+        <v>12.772412375</v>
       </c>
       <c r="P8">
-        <v>89.66259925</v>
+        <v>89.406886625</v>
       </c>
       <c r="Q8">
-        <v>104.06259925</v>
+        <v>103.806886625</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07768984575068816</v>
+        <v>0.07799215191825515</v>
       </c>
       <c r="T8">
-        <v>0.6215924502195942</v>
+        <v>0.6274849601076485</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.43969002964428</v>
+        <v>50.9483057396951</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07561357628397727</v>
+        <v>0.07555794756230771</v>
       </c>
       <c r="C9">
-        <v>544.1926975975808</v>
+        <v>538.6397608792643</v>
       </c>
       <c r="D9">
-        <v>450.0626975975807</v>
+        <v>450.3197608792643</v>
       </c>
       <c r="E9">
-        <v>-238.83</v>
+        <v>-233.02</v>
       </c>
       <c r="F9">
-        <v>40.67</v>
+        <v>46.48</v>
       </c>
       <c r="G9">
         <v>134.8</v>
@@ -2025,28 +2025,28 @@
         <v>104.225</v>
       </c>
       <c r="M9">
-        <v>2.045701</v>
+        <v>2.337944</v>
       </c>
       <c r="N9">
-        <v>102.179299</v>
+        <v>101.887056</v>
       </c>
       <c r="O9">
-        <v>12.772412375</v>
+        <v>12.735882</v>
       </c>
       <c r="P9">
-        <v>89.406886625</v>
+        <v>89.151174</v>
       </c>
       <c r="Q9">
-        <v>103.806886625</v>
+        <v>103.551174</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07799215191825515</v>
+        <v>0.07830102995903013</v>
       </c>
       <c r="T9">
-        <v>0.6274849601076485</v>
+        <v>0.6335055680367477</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.9483057396951</v>
+        <v>44.5797675222332</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07555794756230771</v>
+        <v>0.07550231884063813</v>
       </c>
       <c r="C10">
-        <v>538.6397608792643</v>
+        <v>533.0871179835493</v>
       </c>
       <c r="D10">
-        <v>450.3197608792643</v>
+        <v>450.5771179835493</v>
       </c>
       <c r="E10">
-        <v>-233.02</v>
+        <v>-227.21</v>
       </c>
       <c r="F10">
-        <v>46.48</v>
+        <v>52.29</v>
       </c>
       <c r="G10">
         <v>134.8</v>
@@ -2107,28 +2107,28 @@
         <v>104.225</v>
       </c>
       <c r="M10">
-        <v>2.337944</v>
+        <v>2.630187</v>
       </c>
       <c r="N10">
-        <v>101.887056</v>
+        <v>101.594813</v>
       </c>
       <c r="O10">
-        <v>12.735882</v>
+        <v>12.699351625</v>
       </c>
       <c r="P10">
-        <v>89.151174</v>
+        <v>88.895461375</v>
       </c>
       <c r="Q10">
-        <v>103.551174</v>
+        <v>103.295461375</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07830102995903013</v>
+        <v>0.07861669652817377</v>
       </c>
       <c r="T10">
-        <v>0.6335055680367477</v>
+        <v>0.6396584970192335</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.5797675222332</v>
+        <v>39.62646001976285</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07550231884063813</v>
+        <v>0.07544669011896854</v>
       </c>
       <c r="C11">
-        <v>533.0871179835493</v>
+        <v>527.5347694144813</v>
       </c>
       <c r="D11">
-        <v>450.5771179835493</v>
+        <v>450.8347694144812</v>
       </c>
       <c r="E11">
-        <v>-227.21</v>
+        <v>-221.4</v>
       </c>
       <c r="F11">
-        <v>52.29</v>
+        <v>58.09999999999999</v>
       </c>
       <c r="G11">
         <v>134.8</v>
@@ -2189,28 +2189,28 @@
         <v>104.225</v>
       </c>
       <c r="M11">
-        <v>2.630187</v>
+        <v>2.922429999999999</v>
       </c>
       <c r="N11">
-        <v>101.594813</v>
+        <v>101.30257</v>
       </c>
       <c r="O11">
-        <v>12.699351625</v>
+        <v>12.66282125</v>
       </c>
       <c r="P11">
-        <v>88.895461375</v>
+        <v>88.63974875</v>
       </c>
       <c r="Q11">
-        <v>103.295461375</v>
+        <v>103.03974875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07861669652817377</v>
+        <v>0.07893937790996505</v>
       </c>
       <c r="T11">
-        <v>0.6396584970192335</v>
+        <v>0.6459481577568859</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.62646001976285</v>
+        <v>35.66381401778657</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07544669011896854</v>
+        <v>0.07539106139729895</v>
       </c>
       <c r="C12">
-        <v>527.5347694144813</v>
+        <v>521.9827156772595</v>
       </c>
       <c r="D12">
-        <v>450.8347694144812</v>
+        <v>451.0927156772595</v>
       </c>
       <c r="E12">
-        <v>-221.4</v>
+        <v>-215.59</v>
       </c>
       <c r="F12">
-        <v>58.1</v>
+        <v>63.91</v>
       </c>
       <c r="G12">
         <v>134.8</v>
@@ -2271,28 +2271,28 @@
         <v>104.225</v>
       </c>
       <c r="M12">
-        <v>2.92243</v>
+        <v>3.214673</v>
       </c>
       <c r="N12">
-        <v>101.30257</v>
+        <v>101.010327</v>
       </c>
       <c r="O12">
-        <v>12.66282125</v>
+        <v>12.626290875</v>
       </c>
       <c r="P12">
-        <v>88.63974875</v>
+        <v>88.38403612499999</v>
       </c>
       <c r="Q12">
-        <v>103.03974875</v>
+        <v>102.784036125</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07893937790996505</v>
+        <v>0.07926931055876288</v>
       </c>
       <c r="T12">
-        <v>0.6459481577568859</v>
+        <v>0.6523791591852719</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.66381401778656</v>
+        <v>32.42164910707869</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07539106139729895</v>
+        <v>0.07533543267562939</v>
       </c>
       <c r="C13">
-        <v>521.9827156772595</v>
+        <v>516.43095727824</v>
       </c>
       <c r="D13">
-        <v>451.0927156772595</v>
+        <v>451.3509572782401</v>
       </c>
       <c r="E13">
-        <v>-215.59</v>
+        <v>-209.78</v>
       </c>
       <c r="F13">
-        <v>63.91</v>
+        <v>69.72</v>
       </c>
       <c r="G13">
         <v>134.8</v>
@@ -2353,28 +2353,28 @@
         <v>104.225</v>
       </c>
       <c r="M13">
-        <v>3.214673</v>
+        <v>3.506916</v>
       </c>
       <c r="N13">
-        <v>101.010327</v>
+        <v>100.718084</v>
       </c>
       <c r="O13">
-        <v>12.626290875</v>
+        <v>12.5897605</v>
       </c>
       <c r="P13">
-        <v>88.38403612499999</v>
+        <v>88.12832349999999</v>
       </c>
       <c r="Q13">
-        <v>102.784036125</v>
+        <v>102.5283235</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07926931055876288</v>
+        <v>0.07960674167685158</v>
       </c>
       <c r="T13">
-        <v>0.6523791591852719</v>
+        <v>0.6589563197370303</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.42164910707869</v>
+        <v>29.71984501482214</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07533543267562939</v>
+        <v>0.07527980395395981</v>
       </c>
       <c r="C14">
-        <v>516.43095727824</v>
+        <v>510.8794947249393</v>
       </c>
       <c r="D14">
-        <v>451.3509572782401</v>
+        <v>451.6094947249392</v>
       </c>
       <c r="E14">
-        <v>-209.78</v>
+        <v>-203.97</v>
       </c>
       <c r="F14">
-        <v>69.72</v>
+        <v>75.53</v>
       </c>
       <c r="G14">
         <v>134.8</v>
@@ -2435,28 +2435,28 @@
         <v>104.225</v>
       </c>
       <c r="M14">
-        <v>3.506916</v>
+        <v>3.799159</v>
       </c>
       <c r="N14">
-        <v>100.718084</v>
+        <v>100.425841</v>
       </c>
       <c r="O14">
-        <v>12.5897605</v>
+        <v>12.553230125</v>
       </c>
       <c r="P14">
-        <v>88.12832349999999</v>
+        <v>87.87261087499999</v>
       </c>
       <c r="Q14">
-        <v>102.5283235</v>
+        <v>102.272610875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07960674167685158</v>
+        <v>0.07995192983213771</v>
       </c>
       <c r="T14">
-        <v>0.6589563197370303</v>
+        <v>0.6656846793819325</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.71984501482214</v>
+        <v>27.43370309060505</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07527980395395981</v>
+        <v>0.07522417523229022</v>
       </c>
       <c r="C15">
-        <v>510.8794947249393</v>
+        <v>505.3283285260368</v>
       </c>
       <c r="D15">
-        <v>451.6094947249392</v>
+        <v>451.8683285260368</v>
       </c>
       <c r="E15">
-        <v>-203.97</v>
+        <v>-198.16</v>
       </c>
       <c r="F15">
-        <v>75.53</v>
+        <v>81.34</v>
       </c>
       <c r="G15">
         <v>134.8</v>
@@ -2517,28 +2517,28 @@
         <v>104.225</v>
       </c>
       <c r="M15">
-        <v>3.799159</v>
+        <v>4.091402</v>
       </c>
       <c r="N15">
-        <v>100.425841</v>
+        <v>100.133598</v>
       </c>
       <c r="O15">
-        <v>12.553230125</v>
+        <v>12.51669975</v>
       </c>
       <c r="P15">
-        <v>87.87261087499999</v>
+        <v>87.61689824999999</v>
       </c>
       <c r="Q15">
-        <v>102.272610875</v>
+        <v>102.01689825</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07995192983213771</v>
+        <v>0.08030514561894213</v>
       </c>
       <c r="T15">
-        <v>0.6656846793819325</v>
+        <v>0.6725695125069489</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.43370309060505</v>
+        <v>25.47415286984755</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07522417523229022</v>
+        <v>0.07516854651062066</v>
       </c>
       <c r="C16">
-        <v>505.3283285260368</v>
+        <v>499.7774591913793</v>
       </c>
       <c r="D16">
-        <v>451.8683285260368</v>
+        <v>452.1274591913792</v>
       </c>
       <c r="E16">
-        <v>-198.16</v>
+        <v>-192.35</v>
       </c>
       <c r="F16">
-        <v>81.34</v>
+        <v>87.15000000000002</v>
       </c>
       <c r="G16">
         <v>134.8</v>
@@ -2599,28 +2599,28 @@
         <v>104.225</v>
       </c>
       <c r="M16">
-        <v>4.091402</v>
+        <v>4.383645</v>
       </c>
       <c r="N16">
-        <v>100.133598</v>
+        <v>99.84135499999999</v>
       </c>
       <c r="O16">
-        <v>12.51669975</v>
+        <v>12.480169375</v>
       </c>
       <c r="P16">
-        <v>87.61689824999999</v>
+        <v>87.36118562499999</v>
       </c>
       <c r="Q16">
-        <v>102.01689825</v>
+        <v>101.761185625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08030514561894213</v>
+        <v>0.08066667236543607</v>
       </c>
       <c r="T16">
-        <v>0.6725695125069489</v>
+        <v>0.679616341705495</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.47415286984755</v>
+        <v>23.77587601185771</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07516854651062062</v>
+        <v>0.07511291778895107</v>
       </c>
       <c r="C17">
-        <v>499.7774591913795</v>
+        <v>494.2268872319835</v>
       </c>
       <c r="D17">
-        <v>452.1274591913794</v>
+        <v>452.3868872319836</v>
       </c>
       <c r="E17">
-        <v>-192.35</v>
+        <v>-186.54</v>
       </c>
       <c r="F17">
-        <v>87.14999999999999</v>
+        <v>92.96000000000001</v>
       </c>
       <c r="G17">
         <v>134.8</v>
@@ -2681,28 +2681,28 @@
         <v>104.225</v>
       </c>
       <c r="M17">
-        <v>4.383645</v>
+        <v>4.675888</v>
       </c>
       <c r="N17">
-        <v>99.84135499999999</v>
+        <v>99.54911199999999</v>
       </c>
       <c r="O17">
-        <v>12.480169375</v>
+        <v>12.443639</v>
       </c>
       <c r="P17">
-        <v>87.36118562499999</v>
+        <v>87.10547299999999</v>
       </c>
       <c r="Q17">
-        <v>101.761185625</v>
+        <v>101.505473</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08066667236543604</v>
+        <v>0.08103680689160841</v>
       </c>
       <c r="T17">
-        <v>0.6796163417054948</v>
+        <v>0.6868309525516254</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.77587601185771</v>
+        <v>22.2898837611166</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07511291778895107</v>
+        <v>0.07505728906728149</v>
       </c>
       <c r="C18">
-        <v>494.2268872319835</v>
+        <v>488.67661316004</v>
       </c>
       <c r="D18">
-        <v>452.3868872319836</v>
+        <v>452.64661316004</v>
       </c>
       <c r="E18">
-        <v>-186.54</v>
+        <v>-180.73</v>
       </c>
       <c r="F18">
-        <v>92.96000000000001</v>
+        <v>98.77000000000001</v>
       </c>
       <c r="G18">
         <v>134.8</v>
@@ -2763,28 +2763,28 @@
         <v>104.225</v>
       </c>
       <c r="M18">
-        <v>4.675888</v>
+        <v>4.968131000000001</v>
       </c>
       <c r="N18">
-        <v>99.54911199999999</v>
+        <v>99.25686899999999</v>
       </c>
       <c r="O18">
-        <v>12.443639</v>
+        <v>12.407108625</v>
       </c>
       <c r="P18">
-        <v>87.10547299999999</v>
+        <v>86.84976037499999</v>
       </c>
       <c r="Q18">
-        <v>101.505473</v>
+        <v>101.249760375</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08103680689160841</v>
+        <v>0.08141586032202588</v>
       </c>
       <c r="T18">
-        <v>0.6868309525516254</v>
+        <v>0.694219409442241</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.2898837611166</v>
+        <v>20.97871412810974</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07505728906728149</v>
+        <v>0.07500166034561191</v>
       </c>
       <c r="C19">
-        <v>488.67661316004</v>
+        <v>483.1266374889159</v>
       </c>
       <c r="D19">
-        <v>452.64661316004</v>
+        <v>452.9066374889159</v>
       </c>
       <c r="E19">
-        <v>-180.73</v>
+        <v>-174.92</v>
       </c>
       <c r="F19">
-        <v>98.77000000000001</v>
+        <v>104.58</v>
       </c>
       <c r="G19">
         <v>134.8</v>
@@ -2845,28 +2845,28 @@
         <v>104.225</v>
       </c>
       <c r="M19">
-        <v>4.968131000000001</v>
+        <v>5.260374000000001</v>
       </c>
       <c r="N19">
-        <v>99.25686899999999</v>
+        <v>98.964626</v>
       </c>
       <c r="O19">
-        <v>12.407108625</v>
+        <v>12.37057825</v>
       </c>
       <c r="P19">
-        <v>86.84976037499999</v>
+        <v>86.59404775</v>
       </c>
       <c r="Q19">
-        <v>101.249760375</v>
+        <v>100.99404775</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08141586032202588</v>
+        <v>0.0818041589580633</v>
       </c>
       <c r="T19">
-        <v>0.694219409442241</v>
+        <v>0.7017880725984814</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.97871412810974</v>
+        <v>19.81323000988142</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0750016603456119</v>
+        <v>0.07494603162394234</v>
       </c>
       <c r="C20">
-        <v>483.1266374889159</v>
+        <v>477.5769607331587</v>
       </c>
       <c r="D20">
-        <v>452.9066374889159</v>
+        <v>453.1669607331587</v>
       </c>
       <c r="E20">
-        <v>-174.92</v>
+        <v>-169.11</v>
       </c>
       <c r="F20">
-        <v>104.58</v>
+        <v>110.39</v>
       </c>
       <c r="G20">
         <v>134.8</v>
@@ -2927,28 +2927,28 @@
         <v>104.225</v>
       </c>
       <c r="M20">
-        <v>5.260374</v>
+        <v>5.552617</v>
       </c>
       <c r="N20">
-        <v>98.964626</v>
+        <v>98.672383</v>
       </c>
       <c r="O20">
-        <v>12.37057825</v>
+        <v>12.334047875</v>
       </c>
       <c r="P20">
-        <v>86.59404775</v>
+        <v>86.338335125</v>
       </c>
       <c r="Q20">
-        <v>100.99404775</v>
+        <v>100.738335125</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0818041589580633</v>
+        <v>0.08220204521474361</v>
       </c>
       <c r="T20">
-        <v>0.7017880725984814</v>
+        <v>0.7095436163264807</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.81323000988143</v>
+        <v>18.77042843041398</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07494603162394234</v>
+        <v>0.07489040290227275</v>
       </c>
       <c r="C21">
-        <v>477.5769607331587</v>
+        <v>472.0275834084999</v>
       </c>
       <c r="D21">
-        <v>453.1669607331587</v>
+        <v>453.4275834084999</v>
       </c>
       <c r="E21">
-        <v>-169.11</v>
+        <v>-163.3</v>
       </c>
       <c r="F21">
-        <v>110.39</v>
+        <v>116.2</v>
       </c>
       <c r="G21">
         <v>134.8</v>
@@ -3009,28 +3009,28 @@
         <v>104.225</v>
       </c>
       <c r="M21">
-        <v>5.552617</v>
+        <v>5.84486</v>
       </c>
       <c r="N21">
-        <v>98.672383</v>
+        <v>98.38014</v>
       </c>
       <c r="O21">
-        <v>12.334047875</v>
+        <v>12.2975175</v>
       </c>
       <c r="P21">
-        <v>86.338335125</v>
+        <v>86.0826225</v>
       </c>
       <c r="Q21">
-        <v>100.738335125</v>
+        <v>100.4826225</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08220204521474361</v>
+        <v>0.08260987862784093</v>
       </c>
       <c r="T21">
-        <v>0.7095436163264807</v>
+        <v>0.7174930486476802</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.77042843041398</v>
+        <v>17.83190700889329</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07489040290227275</v>
+        <v>0.07483477418060318</v>
       </c>
       <c r="C22">
-        <v>472.0275834084999</v>
+        <v>466.4785060318576</v>
       </c>
       <c r="D22">
-        <v>453.4275834084999</v>
+        <v>453.6885060318576</v>
       </c>
       <c r="E22">
-        <v>-163.3</v>
+        <v>-157.49</v>
       </c>
       <c r="F22">
-        <v>116.2</v>
+        <v>122.01</v>
       </c>
       <c r="G22">
         <v>134.8</v>
@@ -3091,28 +3091,28 @@
         <v>104.225</v>
       </c>
       <c r="M22">
-        <v>5.84486</v>
+        <v>6.137103</v>
       </c>
       <c r="N22">
-        <v>98.38014</v>
+        <v>98.087897</v>
       </c>
       <c r="O22">
-        <v>12.2975175</v>
+        <v>12.260987125</v>
       </c>
       <c r="P22">
-        <v>86.0826225</v>
+        <v>85.826909875</v>
       </c>
       <c r="Q22">
-        <v>100.4826225</v>
+        <v>100.226909875</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08260987862784093</v>
+        <v>0.08302803693747236</v>
       </c>
       <c r="T22">
-        <v>0.7174930486476802</v>
+        <v>0.7256437324200492</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.83190700889329</v>
+        <v>16.98276857989837</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07483477418060316</v>
+        <v>0.07477914545893359</v>
       </c>
       <c r="C23">
-        <v>466.4785060318576</v>
+        <v>460.9297291213407</v>
       </c>
       <c r="D23">
-        <v>453.6885060318576</v>
+        <v>453.9497291213407</v>
       </c>
       <c r="E23">
-        <v>-157.49</v>
+        <v>-151.68</v>
       </c>
       <c r="F23">
-        <v>122.01</v>
+        <v>127.82</v>
       </c>
       <c r="G23">
         <v>134.8</v>
@@ -3173,28 +3173,28 @@
         <v>104.225</v>
       </c>
       <c r="M23">
-        <v>6.137102999999999</v>
+        <v>6.429346</v>
       </c>
       <c r="N23">
-        <v>98.087897</v>
+        <v>97.795654</v>
       </c>
       <c r="O23">
-        <v>12.260987125</v>
+        <v>12.22445675</v>
       </c>
       <c r="P23">
-        <v>85.826909875</v>
+        <v>85.57119725</v>
       </c>
       <c r="Q23">
-        <v>100.226909875</v>
+        <v>99.97119725</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08302803693747235</v>
+        <v>0.08345691725504306</v>
       </c>
       <c r="T23">
-        <v>0.725643732420049</v>
+        <v>0.7340034080840173</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.98276857989837</v>
+        <v>16.21082455353935</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07477914545893359</v>
+        <v>0.074723516737264</v>
       </c>
       <c r="C24">
-        <v>460.9297291213407</v>
+        <v>455.3812531962523</v>
       </c>
       <c r="D24">
-        <v>453.9497291213407</v>
+        <v>454.2112531962522</v>
       </c>
       <c r="E24">
-        <v>-151.68</v>
+        <v>-145.87</v>
       </c>
       <c r="F24">
-        <v>127.82</v>
+        <v>133.63</v>
       </c>
       <c r="G24">
         <v>134.8</v>
@@ -3255,28 +3255,28 @@
         <v>104.225</v>
       </c>
       <c r="M24">
-        <v>6.429346</v>
+        <v>6.721589</v>
       </c>
       <c r="N24">
-        <v>97.795654</v>
+        <v>97.503411</v>
       </c>
       <c r="O24">
-        <v>12.22445675</v>
+        <v>12.187926375</v>
       </c>
       <c r="P24">
-        <v>85.57119725</v>
+        <v>85.315484625</v>
       </c>
       <c r="Q24">
-        <v>99.97119725</v>
+        <v>99.715484625</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08345691725504306</v>
+        <v>0.08389693732112208</v>
       </c>
       <c r="T24">
-        <v>0.7340034080840173</v>
+        <v>0.7425802181808157</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.21082455353935</v>
+        <v>15.50600609468981</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.074723516737264</v>
+        <v>0.07466788801559443</v>
       </c>
       <c r="C25">
-        <v>455.3812531962523</v>
+        <v>449.8330787770921</v>
       </c>
       <c r="D25">
-        <v>454.2112531962522</v>
+        <v>454.4730787770921</v>
       </c>
       <c r="E25">
-        <v>-145.87</v>
+        <v>-140.06</v>
       </c>
       <c r="F25">
-        <v>133.63</v>
+        <v>139.44</v>
       </c>
       <c r="G25">
         <v>134.8</v>
@@ -3337,28 +3337,28 @@
         <v>104.225</v>
       </c>
       <c r="M25">
-        <v>6.721589</v>
+        <v>7.013832</v>
       </c>
       <c r="N25">
-        <v>97.503411</v>
+        <v>97.211168</v>
       </c>
       <c r="O25">
-        <v>12.187926375</v>
+        <v>12.151396</v>
       </c>
       <c r="P25">
-        <v>85.315484625</v>
+        <v>85.059772</v>
       </c>
       <c r="Q25">
-        <v>99.715484625</v>
+        <v>99.459772</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08389693732112208</v>
+        <v>0.08434853686262424</v>
       </c>
       <c r="T25">
-        <v>0.7425802181808157</v>
+        <v>0.7513827338064775</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.50600609468981</v>
+        <v>14.85992250741107</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07466788801559443</v>
+        <v>0.07461225929392484</v>
       </c>
       <c r="C26">
-        <v>449.8330787770921</v>
+        <v>444.2852063855617</v>
       </c>
       <c r="D26">
-        <v>454.4730787770921</v>
+        <v>454.7352063855617</v>
       </c>
       <c r="E26">
-        <v>-140.06</v>
+        <v>-134.25</v>
       </c>
       <c r="F26">
-        <v>139.44</v>
+        <v>145.25</v>
       </c>
       <c r="G26">
         <v>134.8</v>
@@ -3419,28 +3419,28 @@
         <v>104.225</v>
       </c>
       <c r="M26">
-        <v>7.013832</v>
+        <v>7.306075</v>
       </c>
       <c r="N26">
-        <v>97.211168</v>
+        <v>96.918925</v>
       </c>
       <c r="O26">
-        <v>12.151396</v>
+        <v>12.114865625</v>
       </c>
       <c r="P26">
-        <v>85.059772</v>
+        <v>84.80405937500001</v>
       </c>
       <c r="Q26">
-        <v>99.459772</v>
+        <v>99.20405937500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08434853686262424</v>
+        <v>0.08481217905856644</v>
       </c>
       <c r="T26">
-        <v>0.7513827338064774</v>
+        <v>0.7604199831821566</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.85992250741107</v>
+        <v>14.26552560711463</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07461225929392484</v>
+        <v>0.07455663057225527</v>
       </c>
       <c r="C27">
-        <v>444.2852063855617</v>
+        <v>438.7376365445661</v>
       </c>
       <c r="D27">
-        <v>454.7352063855617</v>
+        <v>454.9976365445661</v>
       </c>
       <c r="E27">
-        <v>-134.25</v>
+        <v>-128.44</v>
       </c>
       <c r="F27">
-        <v>145.25</v>
+        <v>151.06</v>
       </c>
       <c r="G27">
         <v>134.8</v>
@@ -3501,28 +3501,28 @@
         <v>104.225</v>
       </c>
       <c r="M27">
-        <v>7.306075</v>
+        <v>7.598318</v>
       </c>
       <c r="N27">
-        <v>96.918925</v>
+        <v>96.62668199999999</v>
       </c>
       <c r="O27">
-        <v>12.114865625</v>
+        <v>12.07833525</v>
       </c>
       <c r="P27">
-        <v>84.80405937500001</v>
+        <v>84.54834674999999</v>
       </c>
       <c r="Q27">
-        <v>99.20405937500001</v>
+        <v>98.94834675</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08481217905856644</v>
+        <v>0.08528835212466927</v>
       </c>
       <c r="T27">
-        <v>0.7604199831821566</v>
+        <v>0.7697014825409625</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.26552560711463</v>
+        <v>13.71685154530253</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07455663057225527</v>
+        <v>0.07450100185058568</v>
       </c>
       <c r="C28">
-        <v>438.7376365445661</v>
+        <v>433.1903697782187</v>
       </c>
       <c r="D28">
-        <v>454.9976365445661</v>
+        <v>455.2603697782187</v>
       </c>
       <c r="E28">
-        <v>-128.44</v>
+        <v>-122.63</v>
       </c>
       <c r="F28">
-        <v>151.06</v>
+        <v>156.87</v>
       </c>
       <c r="G28">
         <v>134.8</v>
@@ -3583,28 +3583,28 @@
         <v>104.225</v>
       </c>
       <c r="M28">
-        <v>7.598318</v>
+        <v>7.890561</v>
       </c>
       <c r="N28">
-        <v>96.62668199999999</v>
+        <v>96.33443899999999</v>
       </c>
       <c r="O28">
-        <v>12.07833525</v>
+        <v>12.041804875</v>
       </c>
       <c r="P28">
-        <v>84.54834674999999</v>
+        <v>84.29263412499999</v>
       </c>
       <c r="Q28">
-        <v>98.94834675</v>
+        <v>98.692634125</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08528835212466927</v>
+        <v>0.08577757102819956</v>
       </c>
       <c r="T28">
-        <v>0.7697014825409625</v>
+        <v>0.7792372695534342</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.71685154530253</v>
+        <v>13.20882000658762</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07450100185058568</v>
+        <v>0.0748128731289161</v>
       </c>
       <c r="C29">
-        <v>433.1903697782187</v>
+        <v>425.9113137852672</v>
       </c>
       <c r="D29">
-        <v>455.2603697782187</v>
+        <v>453.7913137852672</v>
       </c>
       <c r="E29">
-        <v>-122.63</v>
+        <v>-116.82</v>
       </c>
       <c r="F29">
-        <v>156.87</v>
+        <v>162.68</v>
       </c>
       <c r="G29">
         <v>134.8</v>
@@ -3665,45 +3665,45 @@
         <v>104.225</v>
       </c>
       <c r="M29">
-        <v>7.890561</v>
+        <v>8.426824</v>
       </c>
       <c r="N29">
-        <v>96.33443899999999</v>
+        <v>95.798176</v>
       </c>
       <c r="O29">
-        <v>12.041804875</v>
+        <v>11.974772</v>
       </c>
       <c r="P29">
-        <v>84.29263412499999</v>
+        <v>83.823404</v>
       </c>
       <c r="Q29">
-        <v>98.692634125</v>
+        <v>98.223404</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08577757102819956</v>
+        <v>0.08628037934571681</v>
       </c>
       <c r="T29">
-        <v>0.7792372695534342</v>
+        <v>0.7890379395384745</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.20882000658762</v>
+        <v>12.36824217522521</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0748128731289161</v>
+        <v>0.0747703694072465</v>
       </c>
       <c r="C30">
-        <v>425.9113137852672</v>
+        <v>420.3009674532086</v>
       </c>
       <c r="D30">
-        <v>453.7913137852672</v>
+        <v>453.9909674532087</v>
       </c>
       <c r="E30">
-        <v>-116.82</v>
+        <v>-111.01</v>
       </c>
       <c r="F30">
-        <v>162.68</v>
+        <v>168.49</v>
       </c>
       <c r="G30">
         <v>134.8</v>
@@ -3747,28 +3747,28 @@
         <v>104.225</v>
       </c>
       <c r="M30">
-        <v>8.426824</v>
+        <v>8.727781999999999</v>
       </c>
       <c r="N30">
-        <v>95.798176</v>
+        <v>95.49721799999999</v>
       </c>
       <c r="O30">
-        <v>11.974772</v>
+        <v>11.93715225</v>
       </c>
       <c r="P30">
-        <v>83.823404</v>
+        <v>83.56006574999999</v>
       </c>
       <c r="Q30">
-        <v>98.223404</v>
+        <v>97.96006575</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08628037934571681</v>
+        <v>0.08679735127781199</v>
       </c>
       <c r="T30">
-        <v>0.7890379395384745</v>
+        <v>0.799114684734361</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.36824217522521</v>
+        <v>11.94175106573469</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0747703694072465</v>
+        <v>0.07472786568557693</v>
       </c>
       <c r="C31">
-        <v>420.3009674532086</v>
+        <v>414.6907968809387</v>
       </c>
       <c r="D31">
-        <v>453.9909674532087</v>
+        <v>454.1907968809386</v>
       </c>
       <c r="E31">
-        <v>-111.01</v>
+        <v>-105.2</v>
       </c>
       <c r="F31">
-        <v>168.49</v>
+        <v>174.3</v>
       </c>
       <c r="G31">
         <v>134.8</v>
@@ -3829,28 +3829,28 @@
         <v>104.225</v>
       </c>
       <c r="M31">
-        <v>8.727781999999999</v>
+        <v>9.028739999999999</v>
       </c>
       <c r="N31">
-        <v>95.49721799999999</v>
+        <v>95.19626</v>
       </c>
       <c r="O31">
-        <v>11.93715225</v>
+        <v>11.8995325</v>
       </c>
       <c r="P31">
-        <v>83.56006574999999</v>
+        <v>83.2967275</v>
       </c>
       <c r="Q31">
-        <v>97.96006575</v>
+        <v>97.69672750000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08679735127781199</v>
+        <v>0.08732909383653847</v>
       </c>
       <c r="T31">
-        <v>0.7991146847343609</v>
+        <v>0.8094793369358442</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.94175106573469</v>
+        <v>11.54369269687686</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07472786568557693</v>
+        <v>0.07468536196390735</v>
       </c>
       <c r="C32">
-        <v>414.6907968809387</v>
+        <v>409.0808023006476</v>
       </c>
       <c r="D32">
-        <v>454.1907968809386</v>
+        <v>454.3908023006476</v>
       </c>
       <c r="E32">
-        <v>-105.2</v>
+        <v>-99.39000000000001</v>
       </c>
       <c r="F32">
-        <v>174.3</v>
+        <v>180.11</v>
       </c>
       <c r="G32">
         <v>134.8</v>
@@ -3911,28 +3911,28 @@
         <v>104.225</v>
       </c>
       <c r="M32">
-        <v>9.028739999999999</v>
+        <v>9.329697999999999</v>
       </c>
       <c r="N32">
-        <v>95.19626</v>
+        <v>94.895302</v>
       </c>
       <c r="O32">
-        <v>11.8995325</v>
+        <v>11.86191275</v>
       </c>
       <c r="P32">
-        <v>83.2967275</v>
+        <v>83.03338925</v>
       </c>
       <c r="Q32">
-        <v>97.69672750000001</v>
+        <v>97.43338925</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08732909383653847</v>
+        <v>0.08787624922305415</v>
       </c>
       <c r="T32">
-        <v>0.8094793369358442</v>
+        <v>0.8201444138388199</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.54369269687686</v>
+        <v>11.17131551310664</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07468536196390735</v>
+        <v>0.07464285824223776</v>
       </c>
       <c r="C33">
-        <v>409.0808023006476</v>
+        <v>403.470983944935</v>
       </c>
       <c r="D33">
-        <v>454.3908023006476</v>
+        <v>454.590983944935</v>
       </c>
       <c r="E33">
-        <v>-99.39000000000001</v>
+        <v>-93.57999999999998</v>
       </c>
       <c r="F33">
-        <v>180.11</v>
+        <v>185.92</v>
       </c>
       <c r="G33">
         <v>134.8</v>
@@ -3993,28 +3993,28 @@
         <v>104.225</v>
       </c>
       <c r="M33">
-        <v>9.329697999999999</v>
+        <v>9.630656</v>
       </c>
       <c r="N33">
-        <v>94.895302</v>
+        <v>94.59434399999999</v>
       </c>
       <c r="O33">
-        <v>11.86191275</v>
+        <v>11.824293</v>
       </c>
       <c r="P33">
-        <v>83.03338925</v>
+        <v>82.770051</v>
       </c>
       <c r="Q33">
-        <v>97.43338925</v>
+        <v>97.170051</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08787624922305415</v>
+        <v>0.08843949741505555</v>
       </c>
       <c r="T33">
-        <v>0.8201444138388199</v>
+        <v>0.8311231694742358</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.17131551310664</v>
+        <v>10.82221190332206</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07464285824223776</v>
+        <v>0.07460035452056819</v>
       </c>
       <c r="C34">
-        <v>403.470983944935</v>
+        <v>397.8613420468103</v>
       </c>
       <c r="D34">
-        <v>454.590983944935</v>
+        <v>454.7913420468102</v>
       </c>
       <c r="E34">
-        <v>-93.57999999999998</v>
+        <v>-87.76999999999998</v>
       </c>
       <c r="F34">
-        <v>185.92</v>
+        <v>191.73</v>
       </c>
       <c r="G34">
         <v>134.8</v>
@@ -4075,28 +4075,28 @@
         <v>104.225</v>
       </c>
       <c r="M34">
-        <v>9.630656</v>
+        <v>9.931614000000001</v>
       </c>
       <c r="N34">
-        <v>94.59434399999999</v>
+        <v>94.293386</v>
       </c>
       <c r="O34">
-        <v>11.824293</v>
+        <v>11.78667325</v>
       </c>
       <c r="P34">
-        <v>82.770051</v>
+        <v>82.50671274999999</v>
       </c>
       <c r="Q34">
-        <v>97.170051</v>
+        <v>96.90671275</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08843949741505555</v>
+        <v>0.08901955898592269</v>
       </c>
       <c r="T34">
-        <v>0.8311231694742358</v>
+        <v>0.8424296491584703</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.82221190332206</v>
+        <v>10.49426608806987</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07460035452056819</v>
+        <v>0.07455785079889862</v>
       </c>
       <c r="C35">
-        <v>397.8613420468103</v>
+        <v>392.2518768396941</v>
       </c>
       <c r="D35">
-        <v>454.7913420468102</v>
+        <v>454.9918768396941</v>
       </c>
       <c r="E35">
-        <v>-87.76999999999998</v>
+        <v>-81.95999999999998</v>
       </c>
       <c r="F35">
-        <v>191.73</v>
+        <v>197.54</v>
       </c>
       <c r="G35">
         <v>134.8</v>
@@ -4157,28 +4157,28 @@
         <v>104.225</v>
       </c>
       <c r="M35">
-        <v>9.931614000000001</v>
+        <v>10.232572</v>
       </c>
       <c r="N35">
-        <v>94.293386</v>
+        <v>93.99242799999999</v>
       </c>
       <c r="O35">
-        <v>11.78667325</v>
+        <v>11.7490535</v>
       </c>
       <c r="P35">
-        <v>82.50671274999999</v>
+        <v>82.24337449999999</v>
       </c>
       <c r="Q35">
-        <v>96.90671275</v>
+        <v>96.64337449999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08901955898592269</v>
+        <v>0.08961719818014943</v>
       </c>
       <c r="T35">
-        <v>0.8424296491584703</v>
+        <v>0.8540787494391966</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.49426608806987</v>
+        <v>10.18561120312664</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07455785079889862</v>
+        <v>0.07451534707722902</v>
       </c>
       <c r="C36">
-        <v>392.2518768396941</v>
+        <v>386.6425885574191</v>
       </c>
       <c r="D36">
-        <v>454.9918768396941</v>
+        <v>455.1925885574191</v>
       </c>
       <c r="E36">
-        <v>-81.95999999999998</v>
+        <v>-76.14999999999998</v>
       </c>
       <c r="F36">
-        <v>197.54</v>
+        <v>203.35</v>
       </c>
       <c r="G36">
         <v>134.8</v>
@@ -4239,28 +4239,28 @@
         <v>104.225</v>
       </c>
       <c r="M36">
-        <v>10.232572</v>
+        <v>10.53353</v>
       </c>
       <c r="N36">
-        <v>93.99242799999999</v>
+        <v>93.69147</v>
       </c>
       <c r="O36">
-        <v>11.7490535</v>
+        <v>11.71143375</v>
       </c>
       <c r="P36">
-        <v>82.24337449999999</v>
+        <v>81.98003625</v>
       </c>
       <c r="Q36">
-        <v>96.64337449999999</v>
+        <v>96.38003625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08961719818014943</v>
+        <v>0.09023322627266006</v>
       </c>
       <c r="T36">
-        <v>0.8540787494391966</v>
+        <v>0.8660862835747145</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.18561120312664</v>
+        <v>9.894593740180166</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07451534707722902</v>
+        <v>0.07500834335555945</v>
       </c>
       <c r="C37">
-        <v>386.6425885574191</v>
+        <v>378.5153834282265</v>
       </c>
       <c r="D37">
-        <v>455.1925885574191</v>
+        <v>452.8753834282264</v>
       </c>
       <c r="E37">
-        <v>-76.14999999999998</v>
+        <v>-70.33999999999997</v>
       </c>
       <c r="F37">
-        <v>203.35</v>
+        <v>209.16</v>
       </c>
       <c r="G37">
         <v>134.8</v>
@@ -4321,45 +4321,45 @@
         <v>104.225</v>
       </c>
       <c r="M37">
-        <v>10.53353</v>
+        <v>11.19006</v>
       </c>
       <c r="N37">
-        <v>93.69147</v>
+        <v>93.03493999999999</v>
       </c>
       <c r="O37">
-        <v>11.71143375</v>
+        <v>11.6293675</v>
       </c>
       <c r="P37">
-        <v>81.98003625</v>
+        <v>81.40557249999999</v>
       </c>
       <c r="Q37">
-        <v>96.38003625</v>
+        <v>95.8055725</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09023322627266006</v>
+        <v>0.09086850524306164</v>
       </c>
       <c r="T37">
-        <v>0.8660862835747145</v>
+        <v>0.8784690531519673</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.894593740180166</v>
+        <v>9.314069808383511</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07500834335555945</v>
+        <v>0.07498071463388988</v>
       </c>
       <c r="C38">
-        <v>378.5153834282265</v>
+        <v>372.8346210869609</v>
       </c>
       <c r="D38">
-        <v>452.8753834282264</v>
+        <v>453.0046210869609</v>
       </c>
       <c r="E38">
-        <v>-70.34</v>
+        <v>-64.53</v>
       </c>
       <c r="F38">
-        <v>209.16</v>
+        <v>214.97</v>
       </c>
       <c r="G38">
         <v>134.8</v>
@@ -4403,28 +4403,28 @@
         <v>104.225</v>
       </c>
       <c r="M38">
-        <v>11.19006</v>
+        <v>11.500895</v>
       </c>
       <c r="N38">
-        <v>93.03493999999999</v>
+        <v>92.72410499999999</v>
       </c>
       <c r="O38">
-        <v>11.6293675</v>
+        <v>11.590513125</v>
       </c>
       <c r="P38">
-        <v>81.40557249999999</v>
+        <v>81.13359187499999</v>
       </c>
       <c r="Q38">
-        <v>95.8055725</v>
+        <v>95.533591875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09086850524306164</v>
+        <v>0.0915239517998252</v>
       </c>
       <c r="T38">
-        <v>0.8784690531519673</v>
+        <v>0.8912449265253234</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.314069808383511</v>
+        <v>9.062338191940714</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07498071463388988</v>
+        <v>0.07495308591222029</v>
       </c>
       <c r="C39">
-        <v>372.8346210869609</v>
+        <v>367.1539325282006</v>
       </c>
       <c r="D39">
-        <v>453.0046210869609</v>
+        <v>453.1339325282006</v>
       </c>
       <c r="E39">
-        <v>-64.53</v>
+        <v>-58.72</v>
       </c>
       <c r="F39">
-        <v>214.97</v>
+        <v>220.78</v>
       </c>
       <c r="G39">
         <v>134.8</v>
@@ -4485,28 +4485,28 @@
         <v>104.225</v>
       </c>
       <c r="M39">
-        <v>11.500895</v>
+        <v>11.81173</v>
       </c>
       <c r="N39">
-        <v>92.72410499999999</v>
+        <v>92.41327</v>
       </c>
       <c r="O39">
-        <v>11.590513125</v>
+        <v>11.55165875</v>
       </c>
       <c r="P39">
-        <v>81.13359187499999</v>
+        <v>80.86161125</v>
       </c>
       <c r="Q39">
-        <v>95.533591875</v>
+        <v>95.26161125</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0915239517998252</v>
+        <v>0.09220054179390369</v>
       </c>
       <c r="T39">
-        <v>0.8912449265253234</v>
+        <v>0.9044329248462071</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.062338191940714</v>
+        <v>8.823855607942274</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07495308591222029</v>
+        <v>0.07492545719055071</v>
       </c>
       <c r="C40">
-        <v>367.1539325282006</v>
+        <v>361.4733178151479</v>
       </c>
       <c r="D40">
-        <v>453.1339325282006</v>
+        <v>453.2633178151479</v>
       </c>
       <c r="E40">
-        <v>-58.72</v>
+        <v>-52.91</v>
       </c>
       <c r="F40">
-        <v>220.78</v>
+        <v>226.59</v>
       </c>
       <c r="G40">
         <v>134.8</v>
@@ -4567,28 +4567,28 @@
         <v>104.225</v>
       </c>
       <c r="M40">
-        <v>11.81173</v>
+        <v>12.122565</v>
       </c>
       <c r="N40">
-        <v>92.41327</v>
+        <v>92.102435</v>
       </c>
       <c r="O40">
-        <v>11.55165875</v>
+        <v>11.512804375</v>
       </c>
       <c r="P40">
-        <v>80.86161125</v>
+        <v>80.589630625</v>
       </c>
       <c r="Q40">
-        <v>95.26161125</v>
+        <v>94.989630625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09220054179390369</v>
+        <v>0.09289931506647658</v>
       </c>
       <c r="T40">
-        <v>0.9044329248462071</v>
+        <v>0.9180533165546608</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.823855607942274</v>
+        <v>8.597602900046319</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07492545719055071</v>
+        <v>0.07489782846888114</v>
       </c>
       <c r="C41">
-        <v>361.4733178151479</v>
+        <v>355.7927770110772</v>
       </c>
       <c r="D41">
-        <v>453.2633178151479</v>
+        <v>453.3927770110772</v>
       </c>
       <c r="E41">
-        <v>-52.91</v>
+        <v>-47.09999999999999</v>
       </c>
       <c r="F41">
-        <v>226.59</v>
+        <v>232.4</v>
       </c>
       <c r="G41">
         <v>134.8</v>
@@ -4649,28 +4649,28 @@
         <v>104.225</v>
       </c>
       <c r="M41">
-        <v>12.122565</v>
+        <v>12.4334</v>
       </c>
       <c r="N41">
-        <v>92.102435</v>
+        <v>91.79159999999999</v>
       </c>
       <c r="O41">
-        <v>11.512804375</v>
+        <v>11.47395</v>
       </c>
       <c r="P41">
-        <v>80.589630625</v>
+        <v>80.31764999999999</v>
       </c>
       <c r="Q41">
-        <v>94.989630625</v>
+        <v>94.71764999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09289931506647658</v>
+        <v>0.09362138078146856</v>
       </c>
       <c r="T41">
-        <v>0.9180533165546608</v>
+        <v>0.9321277213200632</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.597602900046319</v>
+        <v>8.382662827545159</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07489782846888114</v>
+        <v>0.07487019974721155</v>
       </c>
       <c r="C42">
-        <v>355.7927770110772</v>
+        <v>350.1123101793355</v>
       </c>
       <c r="D42">
-        <v>453.3927770110772</v>
+        <v>453.5223101793355</v>
       </c>
       <c r="E42">
-        <v>-47.09999999999999</v>
+        <v>-41.28999999999999</v>
       </c>
       <c r="F42">
-        <v>232.4</v>
+        <v>238.21</v>
       </c>
       <c r="G42">
         <v>134.8</v>
@@ -4731,28 +4731,28 @@
         <v>104.225</v>
       </c>
       <c r="M42">
-        <v>12.4334</v>
+        <v>12.744235</v>
       </c>
       <c r="N42">
-        <v>91.79159999999999</v>
+        <v>91.48076499999999</v>
       </c>
       <c r="O42">
-        <v>11.47395</v>
+        <v>11.435095625</v>
       </c>
       <c r="P42">
-        <v>80.31764999999999</v>
+        <v>80.04566937499999</v>
       </c>
       <c r="Q42">
-        <v>94.71764999999999</v>
+        <v>94.44566937499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09362138078146856</v>
+        <v>0.09436792330035856</v>
       </c>
       <c r="T42">
-        <v>0.9321277213200632</v>
+        <v>0.9466792245520891</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.382662827545159</v>
+        <v>8.178207636629423</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07487019974721155</v>
+        <v>0.07484257102554197</v>
       </c>
       <c r="C43">
-        <v>350.1123101793355</v>
+        <v>344.4319173833419</v>
       </c>
       <c r="D43">
-        <v>453.5223101793355</v>
+        <v>453.6519173833419</v>
       </c>
       <c r="E43">
-        <v>-41.28999999999999</v>
+        <v>-35.47999999999999</v>
       </c>
       <c r="F43">
-        <v>238.21</v>
+        <v>244.02</v>
       </c>
       <c r="G43">
         <v>134.8</v>
@@ -4813,28 +4813,28 @@
         <v>104.225</v>
       </c>
       <c r="M43">
-        <v>12.744235</v>
+        <v>13.05507</v>
       </c>
       <c r="N43">
-        <v>91.48076499999999</v>
+        <v>91.16992999999999</v>
       </c>
       <c r="O43">
-        <v>11.435095625</v>
+        <v>11.39624125</v>
       </c>
       <c r="P43">
-        <v>80.04566937499999</v>
+        <v>79.77368874999999</v>
       </c>
       <c r="Q43">
-        <v>94.44566937499999</v>
+        <v>94.17368875</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09436792330035856</v>
+        <v>0.09514020866472754</v>
       </c>
       <c r="T43">
-        <v>0.9466792245520891</v>
+        <v>0.9617325037576332</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.178207636629423</v>
+        <v>7.983488407185867</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07484257102554198</v>
+        <v>0.07481494230387239</v>
       </c>
       <c r="C44">
-        <v>344.4319173833419</v>
+        <v>338.7515986865881</v>
       </c>
       <c r="D44">
-        <v>453.6519173833418</v>
+        <v>453.7815986865881</v>
       </c>
       <c r="E44">
-        <v>-35.48000000000002</v>
+        <v>-29.67000000000002</v>
       </c>
       <c r="F44">
-        <v>244.02</v>
+        <v>249.83</v>
       </c>
       <c r="G44">
         <v>134.8</v>
@@ -4895,28 +4895,28 @@
         <v>104.225</v>
       </c>
       <c r="M44">
-        <v>13.05507</v>
+        <v>13.365905</v>
       </c>
       <c r="N44">
-        <v>91.16992999999999</v>
+        <v>90.859095</v>
       </c>
       <c r="O44">
-        <v>11.39624125</v>
+        <v>11.357386875</v>
       </c>
       <c r="P44">
-        <v>79.77368874999999</v>
+        <v>79.50170812499999</v>
       </c>
       <c r="Q44">
-        <v>94.17368875</v>
+        <v>93.901708125</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09514020866472754</v>
+        <v>0.09593959176117964</v>
       </c>
       <c r="T44">
-        <v>0.9617325037576331</v>
+        <v>0.9773139681984594</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.983488407185868</v>
+        <v>7.797825886088521</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07481494230387239</v>
+        <v>0.07478731358220282</v>
       </c>
       <c r="C45">
-        <v>338.7515986865881</v>
+        <v>333.0713541526387</v>
       </c>
       <c r="D45">
-        <v>453.7815986865881</v>
+        <v>453.9113541526386</v>
       </c>
       <c r="E45">
-        <v>-29.67000000000002</v>
+        <v>-23.85999999999999</v>
       </c>
       <c r="F45">
-        <v>249.83</v>
+        <v>255.64</v>
       </c>
       <c r="G45">
         <v>134.8</v>
@@ -4977,28 +4977,28 @@
         <v>104.225</v>
       </c>
       <c r="M45">
-        <v>13.365905</v>
+        <v>13.67674</v>
       </c>
       <c r="N45">
-        <v>90.859095</v>
+        <v>90.54826</v>
       </c>
       <c r="O45">
-        <v>11.357386875</v>
+        <v>11.3185325</v>
       </c>
       <c r="P45">
-        <v>79.50170812499999</v>
+        <v>79.2297275</v>
       </c>
       <c r="Q45">
-        <v>93.901708125</v>
+        <v>93.6297275</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09593959176117964</v>
+        <v>0.09676752425393359</v>
       </c>
       <c r="T45">
-        <v>0.9773139681984594</v>
+        <v>0.9934519135121724</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.797825886088521</v>
+        <v>7.6206025704956</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07478731358220282</v>
+        <v>0.07507468486053323</v>
       </c>
       <c r="C46">
-        <v>333.0713541526387</v>
+        <v>325.9153615890207</v>
       </c>
       <c r="D46">
-        <v>453.9113541526386</v>
+        <v>452.5653615890208</v>
       </c>
       <c r="E46">
-        <v>-23.85999999999999</v>
+        <v>-18.05000000000001</v>
       </c>
       <c r="F46">
-        <v>255.64</v>
+        <v>261.45</v>
       </c>
       <c r="G46">
         <v>134.8</v>
@@ -5059,45 +5059,45 @@
         <v>104.225</v>
       </c>
       <c r="M46">
-        <v>13.67674</v>
+        <v>14.196735</v>
       </c>
       <c r="N46">
-        <v>90.54826</v>
+        <v>90.02826499999999</v>
       </c>
       <c r="O46">
-        <v>11.3185325</v>
+        <v>11.253533125</v>
       </c>
       <c r="P46">
-        <v>79.2297275</v>
+        <v>78.77473187499999</v>
       </c>
       <c r="Q46">
-        <v>93.6297275</v>
+        <v>93.17473187499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09676752425393359</v>
+        <v>0.09762556338278769</v>
       </c>
       <c r="T46">
-        <v>0.9934519135121724</v>
+        <v>1.01017669320093</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.6206025704956</v>
+        <v>7.34147675504262</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07507468486053323</v>
+        <v>0.07505405613886365</v>
       </c>
       <c r="C47">
-        <v>325.9153615890207</v>
+        <v>320.2017166069515</v>
       </c>
       <c r="D47">
-        <v>452.5653615890208</v>
+        <v>452.6617166069515</v>
       </c>
       <c r="E47">
-        <v>-18.05000000000001</v>
+        <v>-12.24000000000001</v>
       </c>
       <c r="F47">
-        <v>261.45</v>
+        <v>267.26</v>
       </c>
       <c r="G47">
         <v>134.8</v>
@@ -5141,28 +5141,28 @@
         <v>104.225</v>
       </c>
       <c r="M47">
-        <v>14.196735</v>
+        <v>14.512218</v>
       </c>
       <c r="N47">
-        <v>90.02826499999999</v>
+        <v>89.71278199999999</v>
       </c>
       <c r="O47">
-        <v>11.253533125</v>
+        <v>11.21409775</v>
       </c>
       <c r="P47">
-        <v>78.77473187499999</v>
+        <v>78.49868425</v>
       </c>
       <c r="Q47">
-        <v>93.17473187499999</v>
+        <v>92.89868425</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09762556338278769</v>
+        <v>0.09851538173863639</v>
       </c>
       <c r="T47">
-        <v>1.01017669320093</v>
+        <v>1.027520909174455</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.34147675504262</v>
+        <v>7.181879434280824</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07505405613886365</v>
+        <v>0.07503342741719407</v>
       </c>
       <c r="C48">
-        <v>320.2017166069515</v>
+        <v>314.4881126632267</v>
       </c>
       <c r="D48">
-        <v>452.6617166069515</v>
+        <v>452.7581126632266</v>
       </c>
       <c r="E48">
-        <v>-12.24000000000001</v>
+        <v>-6.430000000000007</v>
       </c>
       <c r="F48">
-        <v>267.26</v>
+        <v>273.07</v>
       </c>
       <c r="G48">
         <v>134.8</v>
@@ -5223,28 +5223,28 @@
         <v>104.225</v>
       </c>
       <c r="M48">
-        <v>14.512218</v>
+        <v>14.827701</v>
       </c>
       <c r="N48">
-        <v>89.71278199999999</v>
+        <v>89.39729899999999</v>
       </c>
       <c r="O48">
-        <v>11.21409775</v>
+        <v>11.174662375</v>
       </c>
       <c r="P48">
-        <v>78.49868425</v>
+        <v>78.22263662499999</v>
       </c>
       <c r="Q48">
-        <v>92.89868425</v>
+        <v>92.622636625</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09851538173863639</v>
+        <v>0.09943877814564919</v>
       </c>
       <c r="T48">
-        <v>1.027520909174455</v>
+        <v>1.045519623863963</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.181879434280824</v>
+        <v>7.029073488870594</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07503342741719407</v>
+        <v>0.07501279869552449</v>
       </c>
       <c r="C49">
-        <v>314.4881126632267</v>
+        <v>308.7745497840697</v>
       </c>
       <c r="D49">
-        <v>452.7581126632266</v>
+        <v>452.8545497840697</v>
       </c>
       <c r="E49">
-        <v>-6.430000000000007</v>
+        <v>-0.6200000000000045</v>
       </c>
       <c r="F49">
-        <v>273.07</v>
+        <v>278.88</v>
       </c>
       <c r="G49">
         <v>134.8</v>
@@ -5305,28 +5305,28 @@
         <v>104.225</v>
       </c>
       <c r="M49">
-        <v>14.827701</v>
+        <v>15.143184</v>
       </c>
       <c r="N49">
-        <v>89.39729899999999</v>
+        <v>89.08181599999999</v>
       </c>
       <c r="O49">
-        <v>11.174662375</v>
+        <v>11.135227</v>
       </c>
       <c r="P49">
-        <v>78.22263662499999</v>
+        <v>77.94658899999999</v>
       </c>
       <c r="Q49">
-        <v>92.622636625</v>
+        <v>92.34658899999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09943877814564919</v>
+        <v>0.1003976897990856</v>
       </c>
       <c r="T49">
-        <v>1.045519623863963</v>
+        <v>1.06421059681076</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.029073488870594</v>
+        <v>6.882634457852456</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07501279869552449</v>
+        <v>0.07499216997385491</v>
       </c>
       <c r="C50">
-        <v>308.7745497840697</v>
+        <v>303.0610279957263</v>
       </c>
       <c r="D50">
-        <v>452.8545497840697</v>
+        <v>452.9510279957263</v>
       </c>
       <c r="E50">
-        <v>-0.6200000000000045</v>
+        <v>5.189999999999998</v>
       </c>
       <c r="F50">
-        <v>278.88</v>
+        <v>284.69</v>
       </c>
       <c r="G50">
         <v>134.8</v>
@@ -5387,28 +5387,28 @@
         <v>104.225</v>
       </c>
       <c r="M50">
-        <v>15.143184</v>
+        <v>15.458667</v>
       </c>
       <c r="N50">
-        <v>89.08181599999999</v>
+        <v>88.76633299999999</v>
       </c>
       <c r="O50">
-        <v>11.135227</v>
+        <v>11.095791625</v>
       </c>
       <c r="P50">
-        <v>77.94658899999999</v>
+        <v>77.67054137499998</v>
       </c>
       <c r="Q50">
-        <v>92.34658899999999</v>
+        <v>92.07054137499999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1003976897990855</v>
+        <v>0.1013942058310881</v>
       </c>
       <c r="T50">
-        <v>1.06421059681076</v>
+        <v>1.083634549088804</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.882634457852456</v>
+        <v>6.742172530141182</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07499216997385491</v>
+        <v>0.07497154125218533</v>
       </c>
       <c r="C51">
-        <v>303.0610279957263</v>
+        <v>297.3475473244648</v>
       </c>
       <c r="D51">
-        <v>452.9510279957263</v>
+        <v>453.0475473244647</v>
       </c>
       <c r="E51">
-        <v>5.189999999999998</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>284.69</v>
+        <v>290.5</v>
       </c>
       <c r="G51">
         <v>134.8</v>
@@ -5469,28 +5469,28 @@
         <v>104.225</v>
       </c>
       <c r="M51">
-        <v>15.458667</v>
+        <v>15.77415</v>
       </c>
       <c r="N51">
-        <v>88.76633299999999</v>
+        <v>88.45084999999999</v>
       </c>
       <c r="O51">
-        <v>11.095791625</v>
+        <v>11.05635625</v>
       </c>
       <c r="P51">
-        <v>77.67054137499998</v>
+        <v>77.39449375</v>
       </c>
       <c r="Q51">
-        <v>92.07054137499999</v>
+        <v>91.79449375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1013942058310881</v>
+        <v>0.1024305825043706</v>
       </c>
       <c r="T51">
-        <v>1.083634549088804</v>
+        <v>1.103835459457969</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.742172530141182</v>
+        <v>6.607329079538358</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07497154125218533</v>
+        <v>0.07495091253051575</v>
       </c>
       <c r="C52">
-        <v>297.3475473244648</v>
+        <v>291.6341077965755</v>
       </c>
       <c r="D52">
-        <v>453.0475473244647</v>
+        <v>453.1441077965754</v>
       </c>
       <c r="E52">
-        <v>11</v>
+        <v>16.81</v>
       </c>
       <c r="F52">
-        <v>290.5</v>
+        <v>296.31</v>
       </c>
       <c r="G52">
         <v>134.8</v>
@@ -5551,28 +5551,28 @@
         <v>104.225</v>
       </c>
       <c r="M52">
-        <v>15.77415</v>
+        <v>16.089633</v>
       </c>
       <c r="N52">
-        <v>88.45084999999999</v>
+        <v>88.135367</v>
       </c>
       <c r="O52">
-        <v>11.05635625</v>
+        <v>11.016920875</v>
       </c>
       <c r="P52">
-        <v>77.39449375</v>
+        <v>77.11844612500001</v>
       </c>
       <c r="Q52">
-        <v>91.79449375</v>
+        <v>91.51844612500001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1024305825043706</v>
+        <v>0.1035092602663587</v>
       </c>
       <c r="T52">
-        <v>1.103835459457969</v>
+        <v>1.124860896780978</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.607329079538358</v>
+        <v>6.477773607390549</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07495091253051575</v>
+        <v>0.07493028380884617</v>
       </c>
       <c r="C53">
-        <v>291.6341077965755</v>
+        <v>285.9207094383713</v>
       </c>
       <c r="D53">
-        <v>453.1441077965754</v>
+        <v>453.2407094383714</v>
       </c>
       <c r="E53">
-        <v>16.81</v>
+        <v>22.62</v>
       </c>
       <c r="F53">
-        <v>296.31</v>
+        <v>302.12</v>
       </c>
       <c r="G53">
         <v>134.8</v>
@@ -5633,28 +5633,28 @@
         <v>104.225</v>
       </c>
       <c r="M53">
-        <v>16.089633</v>
+        <v>16.405116</v>
       </c>
       <c r="N53">
-        <v>88.135367</v>
+        <v>87.819884</v>
       </c>
       <c r="O53">
-        <v>11.016920875</v>
+        <v>10.9774855</v>
       </c>
       <c r="P53">
-        <v>77.11844612500001</v>
+        <v>76.8423985</v>
       </c>
       <c r="Q53">
-        <v>91.51844612500001</v>
+        <v>91.24239850000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1035092602663587</v>
+        <v>0.1046328829350962</v>
       </c>
       <c r="T53">
-        <v>1.124860896780978</v>
+        <v>1.146762393992446</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.477773607390549</v>
+        <v>6.353201038017652</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07493028380884617</v>
+        <v>0.07490965508717659</v>
       </c>
       <c r="C54">
-        <v>285.9207094383713</v>
+        <v>280.2073522761879</v>
       </c>
       <c r="D54">
-        <v>453.2407094383714</v>
+        <v>453.3373522761879</v>
       </c>
       <c r="E54">
-        <v>22.62</v>
+        <v>28.43000000000001</v>
       </c>
       <c r="F54">
-        <v>302.12</v>
+        <v>307.93</v>
       </c>
       <c r="G54">
         <v>134.8</v>
@@ -5715,28 +5715,28 @@
         <v>104.225</v>
       </c>
       <c r="M54">
-        <v>16.405116</v>
+        <v>16.720599</v>
       </c>
       <c r="N54">
-        <v>87.819884</v>
+        <v>87.504401</v>
       </c>
       <c r="O54">
-        <v>10.9774855</v>
+        <v>10.938050125</v>
       </c>
       <c r="P54">
-        <v>76.8423985</v>
+        <v>76.566350875</v>
       </c>
       <c r="Q54">
-        <v>91.24239850000001</v>
+        <v>90.966350875</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1046328829350962</v>
+        <v>0.1058043193344183</v>
       </c>
       <c r="T54">
-        <v>1.146762393992446</v>
+        <v>1.169595869808657</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.353201038017652</v>
+        <v>6.233329320319206</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07490965508717659</v>
+        <v>0.07488902636550701</v>
       </c>
       <c r="C55">
-        <v>280.2073522761879</v>
+        <v>274.494036336383</v>
       </c>
       <c r="D55">
-        <v>453.3373522761879</v>
+        <v>453.434036336383</v>
       </c>
       <c r="E55">
-        <v>28.43000000000001</v>
+        <v>34.24000000000001</v>
       </c>
       <c r="F55">
-        <v>307.93</v>
+        <v>313.74</v>
       </c>
       <c r="G55">
         <v>134.8</v>
@@ -5797,28 +5797,28 @@
         <v>104.225</v>
       </c>
       <c r="M55">
-        <v>16.720599</v>
+        <v>17.036082</v>
       </c>
       <c r="N55">
-        <v>87.504401</v>
+        <v>87.188918</v>
       </c>
       <c r="O55">
-        <v>10.938050125</v>
+        <v>10.89861475</v>
       </c>
       <c r="P55">
-        <v>76.566350875</v>
+        <v>76.29030324999999</v>
       </c>
       <c r="Q55">
-        <v>90.966350875</v>
+        <v>90.69030325</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1058043193344183</v>
+        <v>0.1070266877511022</v>
       </c>
       <c r="T55">
-        <v>1.169595869808657</v>
+        <v>1.193422105442964</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.233329320319206</v>
+        <v>6.11789729586885</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07488902636550701</v>
+        <v>0.07534964764383742</v>
       </c>
       <c r="C56">
-        <v>274.494036336383</v>
+        <v>266.5349399347231</v>
       </c>
       <c r="D56">
-        <v>453.434036336383</v>
+        <v>451.2849399347231</v>
       </c>
       <c r="E56">
-        <v>34.24000000000001</v>
+        <v>40.05000000000001</v>
       </c>
       <c r="F56">
-        <v>313.74</v>
+        <v>319.55</v>
       </c>
       <c r="G56">
         <v>134.8</v>
@@ -5879,45 +5879,45 @@
         <v>104.225</v>
       </c>
       <c r="M56">
-        <v>17.036082</v>
+        <v>17.671115</v>
       </c>
       <c r="N56">
-        <v>87.188918</v>
+        <v>86.55388499999999</v>
       </c>
       <c r="O56">
-        <v>10.89861475</v>
+        <v>10.819235625</v>
       </c>
       <c r="P56">
-        <v>76.29030324999999</v>
+        <v>75.73464937499999</v>
       </c>
       <c r="Q56">
-        <v>90.69030325</v>
+        <v>90.134649375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1070266877511022</v>
+        <v>0.1083033836529721</v>
       </c>
       <c r="T56">
-        <v>1.193422105442964</v>
+        <v>1.21830728488324</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.125</v>
       </c>
       <c r="W56">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.11789729586885</v>
+        <v>5.898043219117752</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07534964764383742</v>
+        <v>0.07533776892216784</v>
       </c>
       <c r="C57">
-        <v>266.5349399347231</v>
+        <v>260.7801059248116</v>
       </c>
       <c r="D57">
-        <v>451.2849399347231</v>
+        <v>451.3401059248116</v>
       </c>
       <c r="E57">
-        <v>40.05000000000001</v>
+        <v>45.86000000000001</v>
       </c>
       <c r="F57">
-        <v>319.55</v>
+        <v>325.36</v>
       </c>
       <c r="G57">
         <v>134.8</v>
@@ -5961,28 +5961,28 @@
         <v>104.225</v>
       </c>
       <c r="M57">
-        <v>17.671115</v>
+        <v>17.992408</v>
       </c>
       <c r="N57">
-        <v>86.55388499999999</v>
+        <v>86.232592</v>
       </c>
       <c r="O57">
-        <v>10.819235625</v>
+        <v>10.779074</v>
       </c>
       <c r="P57">
-        <v>75.73464937499999</v>
+        <v>75.453518</v>
       </c>
       <c r="Q57">
-        <v>90.134649375</v>
+        <v>89.85351800000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1083033836529721</v>
+        <v>0.1096381111867451</v>
       </c>
       <c r="T57">
-        <v>1.21830728488324</v>
+        <v>1.244323608843529</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.898043219117752</v>
+        <v>5.792721018776364</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07533776892216784</v>
+        <v>0.07532589020049826</v>
       </c>
       <c r="C58">
-        <v>260.7801059248116</v>
+        <v>255.0252854037549</v>
       </c>
       <c r="D58">
-        <v>451.3401059248116</v>
+        <v>451.3952854037549</v>
       </c>
       <c r="E58">
-        <v>45.86000000000001</v>
+        <v>51.67000000000002</v>
       </c>
       <c r="F58">
-        <v>325.36</v>
+        <v>331.17</v>
       </c>
       <c r="G58">
         <v>134.8</v>
@@ -6043,28 +6043,28 @@
         <v>104.225</v>
       </c>
       <c r="M58">
-        <v>17.992408</v>
+        <v>18.313701</v>
       </c>
       <c r="N58">
-        <v>86.232592</v>
+        <v>85.91129899999999</v>
       </c>
       <c r="O58">
-        <v>10.779074</v>
+        <v>10.738912375</v>
       </c>
       <c r="P58">
-        <v>75.453518</v>
+        <v>75.17238662499999</v>
       </c>
       <c r="Q58">
-        <v>89.85351800000001</v>
+        <v>89.57238662499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1096381111867451</v>
+        <v>0.1110349190709262</v>
       </c>
       <c r="T58">
-        <v>1.244323608843529</v>
+        <v>1.271549994383366</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.792721018776364</v>
+        <v>5.691094334236427</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07532589020049826</v>
+        <v>0.07531401147882869</v>
       </c>
       <c r="C59">
-        <v>255.0252854037549</v>
+        <v>249.270478376501</v>
       </c>
       <c r="D59">
-        <v>451.3952854037549</v>
+        <v>451.4504783765011</v>
       </c>
       <c r="E59">
-        <v>51.67000000000002</v>
+        <v>57.48000000000002</v>
       </c>
       <c r="F59">
-        <v>331.17</v>
+        <v>336.98</v>
       </c>
       <c r="G59">
         <v>134.8</v>
@@ -6125,28 +6125,28 @@
         <v>104.225</v>
       </c>
       <c r="M59">
-        <v>18.313701</v>
+        <v>18.634994</v>
       </c>
       <c r="N59">
-        <v>85.91129899999999</v>
+        <v>85.59000599999999</v>
       </c>
       <c r="O59">
-        <v>10.738912375</v>
+        <v>10.69875075</v>
       </c>
       <c r="P59">
-        <v>75.17238662499999</v>
+        <v>74.89125524999999</v>
       </c>
       <c r="Q59">
-        <v>89.57238662499999</v>
+        <v>89.29125524999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1110349190709262</v>
+        <v>0.1124982416162588</v>
       </c>
       <c r="T59">
-        <v>1.271549994383366</v>
+        <v>1.30007287447272</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.691094334236427</v>
+        <v>5.592972018128902</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07531401147882869</v>
+        <v>0.07530213275715909</v>
       </c>
       <c r="C60">
-        <v>249.2704783765011</v>
+        <v>243.5156848480004</v>
       </c>
       <c r="D60">
-        <v>451.4504783765011</v>
+        <v>451.5056848480004</v>
       </c>
       <c r="E60">
-        <v>57.47999999999996</v>
+        <v>63.28999999999996</v>
       </c>
       <c r="F60">
-        <v>336.98</v>
+        <v>342.79</v>
       </c>
       <c r="G60">
         <v>134.8</v>
@@ -6207,28 +6207,28 @@
         <v>104.225</v>
       </c>
       <c r="M60">
-        <v>18.634994</v>
+        <v>18.956287</v>
       </c>
       <c r="N60">
-        <v>85.59000599999999</v>
+        <v>85.26871299999999</v>
       </c>
       <c r="O60">
-        <v>10.69875075</v>
+        <v>10.658589125</v>
       </c>
       <c r="P60">
-        <v>74.89125524999999</v>
+        <v>74.610123875</v>
       </c>
       <c r="Q60">
-        <v>89.29125524999999</v>
+        <v>89.01012387500001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1124982416162588</v>
+        <v>0.1140329457491685</v>
       </c>
       <c r="T60">
-        <v>1.300072874472719</v>
+        <v>1.329987114566431</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.592972018128902</v>
+        <v>5.498175882228413</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07530213275715909</v>
+        <v>0.07529025403548953</v>
       </c>
       <c r="C61">
-        <v>243.5156848480004</v>
+        <v>237.7609048232054</v>
       </c>
       <c r="D61">
-        <v>451.5056848480004</v>
+        <v>451.5609048232054</v>
       </c>
       <c r="E61">
-        <v>63.28999999999996</v>
+        <v>69.09999999999997</v>
       </c>
       <c r="F61">
-        <v>342.79</v>
+        <v>348.6</v>
       </c>
       <c r="G61">
         <v>134.8</v>
@@ -6289,28 +6289,28 @@
         <v>104.225</v>
       </c>
       <c r="M61">
-        <v>18.956287</v>
+        <v>19.27758</v>
       </c>
       <c r="N61">
-        <v>85.26871299999999</v>
+        <v>84.94741999999999</v>
       </c>
       <c r="O61">
-        <v>10.658589125</v>
+        <v>10.6184275</v>
       </c>
       <c r="P61">
-        <v>74.610123875</v>
+        <v>74.3289925</v>
       </c>
       <c r="Q61">
-        <v>89.01012387500001</v>
+        <v>88.7289925</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1140329457491685</v>
+        <v>0.1156443850887238</v>
       </c>
       <c r="T61">
-        <v>1.329987114566431</v>
+        <v>1.361397066664829</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.498175882228413</v>
+        <v>5.406539617524606</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07529025403548953</v>
+        <v>0.07527837531381995</v>
       </c>
       <c r="C62">
-        <v>237.7609048232054</v>
+        <v>232.0061383070716</v>
       </c>
       <c r="D62">
-        <v>451.5609048232054</v>
+        <v>451.6161383070716</v>
       </c>
       <c r="E62">
-        <v>69.09999999999997</v>
+        <v>74.90999999999997</v>
       </c>
       <c r="F62">
-        <v>348.6</v>
+        <v>354.41</v>
       </c>
       <c r="G62">
         <v>134.8</v>
@@ -6371,28 +6371,28 @@
         <v>104.225</v>
       </c>
       <c r="M62">
-        <v>19.27758</v>
+        <v>19.598873</v>
       </c>
       <c r="N62">
-        <v>84.94741999999999</v>
+        <v>84.626127</v>
       </c>
       <c r="O62">
-        <v>10.6184275</v>
+        <v>10.578265875</v>
       </c>
       <c r="P62">
-        <v>74.3289925</v>
+        <v>74.047861125</v>
       </c>
       <c r="Q62">
-        <v>88.7289925</v>
+        <v>88.447861125</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1156443850887238</v>
+        <v>0.1173384623431281</v>
       </c>
       <c r="T62">
-        <v>1.361397066664829</v>
+        <v>1.394417785537503</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.406539617524606</v>
+        <v>5.317907820516006</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07527837531381995</v>
+        <v>0.07526649659215036</v>
       </c>
       <c r="C63">
-        <v>232.0061383070716</v>
+        <v>226.2513853045565</v>
       </c>
       <c r="D63">
-        <v>451.6161383070716</v>
+        <v>451.6713853045565</v>
       </c>
       <c r="E63">
-        <v>74.90999999999997</v>
+        <v>80.71999999999997</v>
       </c>
       <c r="F63">
-        <v>354.41</v>
+        <v>360.22</v>
       </c>
       <c r="G63">
         <v>134.8</v>
@@ -6453,28 +6453,28 @@
         <v>104.225</v>
       </c>
       <c r="M63">
-        <v>19.598873</v>
+        <v>19.920166</v>
       </c>
       <c r="N63">
-        <v>84.626127</v>
+        <v>84.304834</v>
       </c>
       <c r="O63">
-        <v>10.578265875</v>
+        <v>10.53810425</v>
       </c>
       <c r="P63">
-        <v>74.047861125</v>
+        <v>73.76672975</v>
       </c>
       <c r="Q63">
-        <v>88.447861125</v>
+        <v>88.16672975</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1173384623431281</v>
+        <v>0.1191217015582904</v>
       </c>
       <c r="T63">
-        <v>1.394417785537503</v>
+        <v>1.429176436982423</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.317907820516006</v>
+        <v>5.232135113733491</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07526649659215036</v>
+        <v>0.07525461787048079</v>
       </c>
       <c r="C64">
-        <v>226.2513853045565</v>
+        <v>220.4966458206201</v>
       </c>
       <c r="D64">
-        <v>451.6713853045565</v>
+        <v>451.7266458206201</v>
       </c>
       <c r="E64">
-        <v>80.71999999999997</v>
+        <v>86.53000000000003</v>
       </c>
       <c r="F64">
-        <v>360.22</v>
+        <v>366.03</v>
       </c>
       <c r="G64">
         <v>134.8</v>
@@ -6535,28 +6535,28 @@
         <v>104.225</v>
       </c>
       <c r="M64">
-        <v>19.920166</v>
+        <v>20.241459</v>
       </c>
       <c r="N64">
-        <v>84.304834</v>
+        <v>83.98354099999999</v>
       </c>
       <c r="O64">
-        <v>10.53810425</v>
+        <v>10.497942625</v>
       </c>
       <c r="P64">
-        <v>73.76672975</v>
+        <v>73.485598375</v>
       </c>
       <c r="Q64">
-        <v>88.16672975</v>
+        <v>87.885598375</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1191217015582904</v>
+        <v>0.1210013320823805</v>
       </c>
       <c r="T64">
-        <v>1.429176436982423</v>
+        <v>1.465813934451394</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.232135113733491</v>
+        <v>5.149085350023434</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07525461787048079</v>
+        <v>0.07524273914881119</v>
       </c>
       <c r="C65">
-        <v>220.4966458206201</v>
+        <v>214.741919860225</v>
       </c>
       <c r="D65">
-        <v>451.7266458206201</v>
+        <v>451.7819198602251</v>
       </c>
       <c r="E65">
-        <v>86.53000000000003</v>
+        <v>92.34000000000003</v>
       </c>
       <c r="F65">
-        <v>366.03</v>
+        <v>371.84</v>
       </c>
       <c r="G65">
         <v>134.8</v>
@@ -6617,28 +6617,28 @@
         <v>104.225</v>
       </c>
       <c r="M65">
-        <v>20.241459</v>
+        <v>20.562752</v>
       </c>
       <c r="N65">
-        <v>83.98354099999999</v>
+        <v>83.66224799999999</v>
       </c>
       <c r="O65">
-        <v>10.497942625</v>
+        <v>10.457781</v>
       </c>
       <c r="P65">
-        <v>73.485598375</v>
+        <v>73.20446699999999</v>
       </c>
       <c r="Q65">
-        <v>87.885598375</v>
+        <v>87.604467</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1210013320823805</v>
+        <v>0.1229853865244755</v>
       </c>
       <c r="T65">
-        <v>1.465813934451394</v>
+        <v>1.504486848446417</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.149085350023434</v>
+        <v>5.068630891429318</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07524273914881119</v>
+        <v>0.07523086042714164</v>
       </c>
       <c r="C66">
-        <v>214.741919860225</v>
+        <v>208.9872074283359</v>
       </c>
       <c r="D66">
-        <v>451.7819198602251</v>
+        <v>451.8372074283359</v>
       </c>
       <c r="E66">
-        <v>92.34000000000003</v>
+        <v>98.15000000000003</v>
       </c>
       <c r="F66">
-        <v>371.84</v>
+        <v>377.65</v>
       </c>
       <c r="G66">
         <v>134.8</v>
@@ -6699,28 +6699,28 @@
         <v>104.225</v>
       </c>
       <c r="M66">
-        <v>20.562752</v>
+        <v>20.884045</v>
       </c>
       <c r="N66">
-        <v>83.66224799999999</v>
+        <v>83.34095499999999</v>
       </c>
       <c r="O66">
-        <v>10.457781</v>
+        <v>10.417619375</v>
       </c>
       <c r="P66">
-        <v>73.20446699999999</v>
+        <v>72.92333562499999</v>
       </c>
       <c r="Q66">
-        <v>87.604467</v>
+        <v>87.323335625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1229853865244755</v>
+        <v>0.1250828155061189</v>
       </c>
       <c r="T66">
-        <v>1.504486848446417</v>
+        <v>1.545369643241157</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.068630891429318</v>
+        <v>4.990651954638097</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07523086042714164</v>
+        <v>0.07521898170547203</v>
       </c>
       <c r="C67">
-        <v>208.9872074283359</v>
+        <v>203.2325085299203</v>
       </c>
       <c r="D67">
-        <v>451.8372074283359</v>
+        <v>451.8925085299203</v>
       </c>
       <c r="E67">
-        <v>98.15000000000003</v>
+        <v>103.96</v>
       </c>
       <c r="F67">
-        <v>377.65</v>
+        <v>383.46</v>
       </c>
       <c r="G67">
         <v>134.8</v>
@@ -6781,28 +6781,28 @@
         <v>104.225</v>
       </c>
       <c r="M67">
-        <v>20.884045</v>
+        <v>21.205338</v>
       </c>
       <c r="N67">
-        <v>83.34095499999999</v>
+        <v>83.019662</v>
       </c>
       <c r="O67">
-        <v>10.417619375</v>
+        <v>10.37745775</v>
       </c>
       <c r="P67">
-        <v>72.92333562499999</v>
+        <v>72.64220424999999</v>
       </c>
       <c r="Q67">
-        <v>87.323335625</v>
+        <v>87.04220425</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1250828155061189</v>
+        <v>0.1273036226631531</v>
       </c>
       <c r="T67">
-        <v>1.545369643241157</v>
+        <v>1.58865730831794</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.990651954638097</v>
+        <v>4.915036015931459</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07521898170547203</v>
+        <v>0.07520710298380245</v>
       </c>
       <c r="C68">
-        <v>203.2325085299203</v>
+        <v>197.477823169948</v>
       </c>
       <c r="D68">
-        <v>451.8925085299203</v>
+        <v>451.947823169948</v>
       </c>
       <c r="E68">
-        <v>103.96</v>
+        <v>109.77</v>
       </c>
       <c r="F68">
-        <v>383.46</v>
+        <v>389.27</v>
       </c>
       <c r="G68">
         <v>134.8</v>
@@ -6863,28 +6863,28 @@
         <v>104.225</v>
       </c>
       <c r="M68">
-        <v>21.205338</v>
+        <v>21.526631</v>
       </c>
       <c r="N68">
-        <v>83.019662</v>
+        <v>82.69836899999999</v>
       </c>
       <c r="O68">
-        <v>10.37745775</v>
+        <v>10.337296125</v>
       </c>
       <c r="P68">
-        <v>72.64220424999999</v>
+        <v>72.36107287499999</v>
       </c>
       <c r="Q68">
-        <v>87.04220425</v>
+        <v>86.761072875</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1273036226631531</v>
+        <v>0.1296590241933408</v>
       </c>
       <c r="T68">
-        <v>1.58865730831794</v>
+        <v>1.634568468247862</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.915036015931459</v>
+        <v>4.84167726942502</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07520710298380245</v>
+        <v>0.07519522426213288</v>
       </c>
       <c r="C69">
-        <v>197.477823169948</v>
+        <v>191.7231513533908</v>
       </c>
       <c r="D69">
-        <v>451.947823169948</v>
+        <v>452.0031513533909</v>
       </c>
       <c r="E69">
-        <v>109.77</v>
+        <v>115.58</v>
       </c>
       <c r="F69">
-        <v>389.27</v>
+        <v>395.08</v>
       </c>
       <c r="G69">
         <v>134.8</v>
@@ -6945,28 +6945,28 @@
         <v>104.225</v>
       </c>
       <c r="M69">
-        <v>21.526631</v>
+        <v>21.847924</v>
       </c>
       <c r="N69">
-        <v>82.69836899999999</v>
+        <v>82.37707599999999</v>
       </c>
       <c r="O69">
-        <v>10.337296125</v>
+        <v>10.2971345</v>
       </c>
       <c r="P69">
-        <v>72.36107287499999</v>
+        <v>72.07994149999999</v>
       </c>
       <c r="Q69">
-        <v>86.761072875</v>
+        <v>86.4799415</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1296590241933408</v>
+        <v>0.1321616383191653</v>
       </c>
       <c r="T69">
-        <v>1.634568468247862</v>
+        <v>1.683349075673404</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.84167726942502</v>
+        <v>4.770476133109946</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07519522426213288</v>
+        <v>0.0751833455404633</v>
       </c>
       <c r="C70">
-        <v>191.7231513533908</v>
+        <v>185.9684930852239</v>
       </c>
       <c r="D70">
-        <v>452.0031513533909</v>
+        <v>452.0584930852239</v>
       </c>
       <c r="E70">
-        <v>115.58</v>
+        <v>121.39</v>
       </c>
       <c r="F70">
-        <v>395.08</v>
+        <v>400.89</v>
       </c>
       <c r="G70">
         <v>134.8</v>
@@ -7027,28 +7027,28 @@
         <v>104.225</v>
       </c>
       <c r="M70">
-        <v>21.847924</v>
+        <v>22.169217</v>
       </c>
       <c r="N70">
-        <v>82.37707599999999</v>
+        <v>82.05578299999999</v>
       </c>
       <c r="O70">
-        <v>10.2971345</v>
+        <v>10.256972875</v>
       </c>
       <c r="P70">
-        <v>72.07994149999999</v>
+        <v>71.79881012499999</v>
       </c>
       <c r="Q70">
-        <v>86.4799415</v>
+        <v>86.19881012499999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1321616383191653</v>
+        <v>0.1348257114208494</v>
       </c>
       <c r="T70">
-        <v>1.683349075673404</v>
+        <v>1.735276819061883</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.770476133109946</v>
+        <v>4.701338797847483</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0751833455404633</v>
+        <v>0.07517146681879372</v>
       </c>
       <c r="C71">
-        <v>185.9684930852239</v>
+        <v>180.2138483704239</v>
       </c>
       <c r="D71">
-        <v>452.0584930852239</v>
+        <v>452.1138483704239</v>
       </c>
       <c r="E71">
-        <v>121.39</v>
+        <v>127.2</v>
       </c>
       <c r="F71">
-        <v>400.89</v>
+        <v>406.7</v>
       </c>
       <c r="G71">
         <v>134.8</v>
@@ -7109,28 +7109,28 @@
         <v>104.225</v>
       </c>
       <c r="M71">
-        <v>22.169217</v>
+        <v>22.49051</v>
       </c>
       <c r="N71">
-        <v>82.05578299999999</v>
+        <v>81.73448999999999</v>
       </c>
       <c r="O71">
-        <v>10.256972875</v>
+        <v>10.21681125</v>
       </c>
       <c r="P71">
-        <v>71.79881012499999</v>
+        <v>71.51767874999999</v>
       </c>
       <c r="Q71">
-        <v>86.19881012499999</v>
+        <v>85.91767874999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1348257114208494</v>
+        <v>0.1376673893959791</v>
       </c>
       <c r="T71">
-        <v>1.735276819061883</v>
+        <v>1.790666412009595</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.701338797847483</v>
+        <v>4.634176815021091</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07517146681879372</v>
+        <v>0.07515958809712414</v>
       </c>
       <c r="C72">
-        <v>180.2138483704239</v>
+        <v>174.4592172139705</v>
       </c>
       <c r="D72">
-        <v>452.1138483704239</v>
+        <v>452.1692172139705</v>
       </c>
       <c r="E72">
-        <v>127.2</v>
+        <v>133.01</v>
       </c>
       <c r="F72">
-        <v>406.7</v>
+        <v>412.51</v>
       </c>
       <c r="G72">
         <v>134.8</v>
@@ -7191,28 +7191,28 @@
         <v>104.225</v>
       </c>
       <c r="M72">
-        <v>22.49051</v>
+        <v>22.811803</v>
       </c>
       <c r="N72">
-        <v>81.73448999999999</v>
+        <v>81.413197</v>
       </c>
       <c r="O72">
-        <v>10.21681125</v>
+        <v>10.176649625</v>
       </c>
       <c r="P72">
-        <v>71.51767874999999</v>
+        <v>71.236547375</v>
       </c>
       <c r="Q72">
-        <v>85.91767874999999</v>
+        <v>85.63654737500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1376673893959791</v>
+        <v>0.1407050451624971</v>
       </c>
       <c r="T72">
-        <v>1.790666412009595</v>
+        <v>1.849875976884735</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.634176815021091</v>
+        <v>4.568906719034878</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07515958809712414</v>
+        <v>0.07514770937545456</v>
       </c>
       <c r="C73">
-        <v>174.4592172139705</v>
+        <v>168.7045996208457</v>
       </c>
       <c r="D73">
-        <v>452.1692172139705</v>
+        <v>452.2245996208457</v>
       </c>
       <c r="E73">
-        <v>133.01</v>
+        <v>138.82</v>
       </c>
       <c r="F73">
-        <v>412.51</v>
+        <v>418.32</v>
       </c>
       <c r="G73">
         <v>134.8</v>
@@ -7273,28 +7273,28 @@
         <v>104.225</v>
       </c>
       <c r="M73">
-        <v>22.811803</v>
+        <v>23.133096</v>
       </c>
       <c r="N73">
-        <v>81.413197</v>
+        <v>81.091904</v>
       </c>
       <c r="O73">
-        <v>10.176649625</v>
+        <v>10.136488</v>
       </c>
       <c r="P73">
-        <v>71.236547375</v>
+        <v>70.955416</v>
       </c>
       <c r="Q73">
-        <v>85.63654737500001</v>
+        <v>85.35541600000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.140705045162497</v>
+        <v>0.1439596763409091</v>
       </c>
       <c r="T73">
-        <v>1.849875976884735</v>
+        <v>1.913314796393814</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.568906719034878</v>
+        <v>4.505449681270505</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07514770937545456</v>
+        <v>0.07673270565378498</v>
       </c>
       <c r="C74">
-        <v>168.7045996208457</v>
+        <v>155.6227767039701</v>
       </c>
       <c r="D74">
-        <v>452.2245996208457</v>
+        <v>444.95277670397</v>
       </c>
       <c r="E74">
-        <v>138.82</v>
+        <v>144.63</v>
       </c>
       <c r="F74">
-        <v>418.32</v>
+        <v>424.13</v>
       </c>
       <c r="G74">
         <v>134.8</v>
@@ -7355,45 +7355,45 @@
         <v>104.225</v>
       </c>
       <c r="M74">
-        <v>23.133096</v>
+        <v>24.514714</v>
       </c>
       <c r="N74">
-        <v>81.091904</v>
+        <v>79.710286</v>
       </c>
       <c r="O74">
-        <v>10.136488</v>
+        <v>9.96378575</v>
       </c>
       <c r="P74">
-        <v>70.955416</v>
+        <v>69.74650025</v>
       </c>
       <c r="Q74">
-        <v>85.35541600000001</v>
+        <v>84.14650025</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1439596763409091</v>
+        <v>0.1474553913103147</v>
       </c>
       <c r="T74">
-        <v>1.913314796393814</v>
+        <v>1.981452787718379</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.125</v>
       </c>
       <c r="W74">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.505449681270505</v>
+        <v>4.251528286236583</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07673270565378498</v>
+        <v>0.0767427019321154</v>
       </c>
       <c r="C75">
-        <v>155.6227767039701</v>
+        <v>149.7676567046516</v>
       </c>
       <c r="D75">
-        <v>444.95277670397</v>
+        <v>444.9076567046516</v>
       </c>
       <c r="E75">
-        <v>144.63</v>
+        <v>150.44</v>
       </c>
       <c r="F75">
-        <v>424.13</v>
+        <v>429.94</v>
       </c>
       <c r="G75">
         <v>134.8</v>
@@ -7437,28 +7437,28 @@
         <v>104.225</v>
       </c>
       <c r="M75">
-        <v>24.514714</v>
+        <v>24.850532</v>
       </c>
       <c r="N75">
-        <v>79.710286</v>
+        <v>79.37446799999999</v>
       </c>
       <c r="O75">
-        <v>9.96378575</v>
+        <v>9.921808499999999</v>
       </c>
       <c r="P75">
-        <v>69.74650025</v>
+        <v>69.4526595</v>
       </c>
       <c r="Q75">
-        <v>84.14650025</v>
+        <v>83.8526595</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1474553913103147</v>
+        <v>0.1512200074312131</v>
       </c>
       <c r="T75">
-        <v>1.981452787718379</v>
+        <v>2.054832162990989</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.251528286236583</v>
+        <v>4.194075201287441</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0767427019321154</v>
+        <v>0.07675269821044582</v>
       </c>
       <c r="C76">
-        <v>149.7676567046516</v>
+        <v>143.9125458551038</v>
       </c>
       <c r="D76">
-        <v>444.9076567046516</v>
+        <v>444.8625458551037</v>
       </c>
       <c r="E76">
-        <v>150.44</v>
+        <v>156.25</v>
       </c>
       <c r="F76">
-        <v>429.94</v>
+        <v>435.75</v>
       </c>
       <c r="G76">
         <v>134.8</v>
@@ -7519,28 +7519,28 @@
         <v>104.225</v>
       </c>
       <c r="M76">
-        <v>24.850532</v>
+        <v>25.18635</v>
       </c>
       <c r="N76">
-        <v>79.37446799999999</v>
+        <v>79.03864999999999</v>
       </c>
       <c r="O76">
-        <v>9.921808499999999</v>
+        <v>9.879831249999999</v>
       </c>
       <c r="P76">
-        <v>69.4526595</v>
+        <v>69.15881874999999</v>
       </c>
       <c r="Q76">
-        <v>83.8526595</v>
+        <v>83.55881875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1512200074312131</v>
+        <v>0.1552857928417833</v>
       </c>
       <c r="T76">
-        <v>2.054832162990989</v>
+        <v>2.134081888285408</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.194075201287441</v>
+        <v>4.138154198603608</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07675269821044582</v>
+        <v>0.07676269448877623</v>
       </c>
       <c r="C77">
-        <v>143.9125458551038</v>
+        <v>138.0574441525436</v>
       </c>
       <c r="D77">
-        <v>444.8625458551037</v>
+        <v>444.8174441525437</v>
       </c>
       <c r="E77">
-        <v>156.25</v>
+        <v>162.06</v>
       </c>
       <c r="F77">
-        <v>435.75</v>
+        <v>441.56</v>
       </c>
       <c r="G77">
         <v>134.8</v>
@@ -7601,28 +7601,28 @@
         <v>104.225</v>
       </c>
       <c r="M77">
-        <v>25.18635</v>
+        <v>25.522168</v>
       </c>
       <c r="N77">
-        <v>79.03864999999999</v>
+        <v>78.702832</v>
       </c>
       <c r="O77">
-        <v>9.879831249999999</v>
+        <v>9.837854</v>
       </c>
       <c r="P77">
-        <v>69.15881874999999</v>
+        <v>68.86497800000001</v>
       </c>
       <c r="Q77">
-        <v>83.55881875</v>
+        <v>83.26497800000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1552857928417833</v>
+        <v>0.1596903937032343</v>
       </c>
       <c r="T77">
-        <v>2.134081888285408</v>
+        <v>2.219935757354361</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.138154198603608</v>
+        <v>4.083704801253561</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07676269448877623</v>
+        <v>0.07677269076710666</v>
       </c>
       <c r="C78">
-        <v>138.0574441525436</v>
+        <v>132.2023515941895</v>
       </c>
       <c r="D78">
-        <v>444.8174441525437</v>
+        <v>444.7723515941894</v>
       </c>
       <c r="E78">
-        <v>162.06</v>
+        <v>167.87</v>
       </c>
       <c r="F78">
-        <v>441.56</v>
+        <v>447.37</v>
       </c>
       <c r="G78">
         <v>134.8</v>
@@ -7683,28 +7683,28 @@
         <v>104.225</v>
       </c>
       <c r="M78">
-        <v>25.522168</v>
+        <v>25.857986</v>
       </c>
       <c r="N78">
-        <v>78.702832</v>
+        <v>78.367014</v>
       </c>
       <c r="O78">
-        <v>9.837854</v>
+        <v>9.79587675</v>
       </c>
       <c r="P78">
-        <v>68.86497800000001</v>
+        <v>68.57113724999999</v>
       </c>
       <c r="Q78">
-        <v>83.26497800000001</v>
+        <v>82.97113725</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1596903937032343</v>
+        <v>0.1644780033352463</v>
       </c>
       <c r="T78">
-        <v>2.219935757354361</v>
+        <v>2.313255180255397</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.083704801253561</v>
+        <v>4.030669673964554</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07677269076710666</v>
+        <v>0.07917143704543708</v>
       </c>
       <c r="C79">
-        <v>132.2023515941895</v>
+        <v>115.8298043340052</v>
       </c>
       <c r="D79">
-        <v>444.7723515941894</v>
+        <v>434.2098043340052</v>
       </c>
       <c r="E79">
-        <v>167.87</v>
+        <v>173.68</v>
       </c>
       <c r="F79">
-        <v>447.37</v>
+        <v>453.18</v>
       </c>
       <c r="G79">
         <v>134.8</v>
@@ -7765,45 +7765,45 @@
         <v>104.225</v>
       </c>
       <c r="M79">
-        <v>25.857986</v>
+        <v>27.779934</v>
       </c>
       <c r="N79">
-        <v>78.367014</v>
+        <v>76.445066</v>
       </c>
       <c r="O79">
-        <v>9.79587675</v>
+        <v>9.55563325</v>
       </c>
       <c r="P79">
-        <v>68.57113724999999</v>
+        <v>66.88943275</v>
       </c>
       <c r="Q79">
-        <v>82.97113725</v>
+        <v>81.28943275</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1644780033352463</v>
+        <v>0.1697008502065322</v>
       </c>
       <c r="T79">
-        <v>2.313255180255397</v>
+        <v>2.415058187056527</v>
       </c>
       <c r="U79">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V79">
         <v>0.125</v>
       </c>
       <c r="W79">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.030669673964554</v>
+        <v>3.751808769596069</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07917143704543708</v>
+        <v>0.07921205832376749</v>
       </c>
       <c r="C80">
-        <v>115.8298043340052</v>
+        <v>109.8452522013398</v>
       </c>
       <c r="D80">
-        <v>434.2098043340052</v>
+        <v>434.0352522013398</v>
       </c>
       <c r="E80">
-        <v>173.68</v>
+        <v>179.49</v>
       </c>
       <c r="F80">
-        <v>453.18</v>
+        <v>458.99</v>
       </c>
       <c r="G80">
         <v>134.8</v>
@@ -7847,28 +7847,28 @@
         <v>104.225</v>
       </c>
       <c r="M80">
-        <v>27.779934</v>
+        <v>28.136087</v>
       </c>
       <c r="N80">
-        <v>76.445066</v>
+        <v>76.08891299999999</v>
       </c>
       <c r="O80">
-        <v>9.55563325</v>
+        <v>9.511114124999999</v>
       </c>
       <c r="P80">
-        <v>66.88943275</v>
+        <v>66.57779887499998</v>
       </c>
       <c r="Q80">
-        <v>81.28943275</v>
+        <v>80.97779887499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1697008502065322</v>
+        <v>0.1754211110655595</v>
       </c>
       <c r="T80">
-        <v>2.415058187056527</v>
+        <v>2.526556718314908</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.751808769596069</v>
+        <v>3.704317519348017</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07921205832376749</v>
+        <v>0.07925267960209792</v>
       </c>
       <c r="C81">
-        <v>109.8452522013398</v>
+        <v>103.8608403520274</v>
       </c>
       <c r="D81">
-        <v>434.0352522013398</v>
+        <v>433.8608403520274</v>
       </c>
       <c r="E81">
-        <v>179.49</v>
+        <v>185.3</v>
       </c>
       <c r="F81">
-        <v>458.99</v>
+        <v>464.8</v>
       </c>
       <c r="G81">
         <v>134.8</v>
@@ -7929,28 +7929,28 @@
         <v>104.225</v>
       </c>
       <c r="M81">
-        <v>28.136087</v>
+        <v>28.49224</v>
       </c>
       <c r="N81">
-        <v>76.08891299999999</v>
+        <v>75.73275999999998</v>
       </c>
       <c r="O81">
-        <v>9.511114124999999</v>
+        <v>9.466594999999998</v>
       </c>
       <c r="P81">
-        <v>66.57779887499998</v>
+        <v>66.26616499999999</v>
       </c>
       <c r="Q81">
-        <v>80.97779887499999</v>
+        <v>80.66616499999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1754211110655595</v>
+        <v>0.1817133980104896</v>
       </c>
       <c r="T81">
-        <v>2.526556718314908</v>
+        <v>2.649205102699127</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.704317519348017</v>
+        <v>3.658013550356166</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07925267960209792</v>
+        <v>0.07929330088042834</v>
       </c>
       <c r="C82">
-        <v>103.8608403520274</v>
+        <v>97.87656861702237</v>
       </c>
       <c r="D82">
-        <v>433.8608403520274</v>
+        <v>433.6865686170224</v>
       </c>
       <c r="E82">
-        <v>185.3</v>
+        <v>191.11</v>
       </c>
       <c r="F82">
-        <v>464.8</v>
+        <v>470.61</v>
       </c>
       <c r="G82">
         <v>134.8</v>
@@ -8011,28 +8011,28 @@
         <v>104.225</v>
       </c>
       <c r="M82">
-        <v>28.49224</v>
+        <v>28.848393</v>
       </c>
       <c r="N82">
-        <v>75.73275999999998</v>
+        <v>75.37660699999999</v>
       </c>
       <c r="O82">
-        <v>9.466594999999998</v>
+        <v>9.422075874999999</v>
       </c>
       <c r="P82">
-        <v>66.26616499999999</v>
+        <v>65.95453112499999</v>
       </c>
       <c r="Q82">
-        <v>80.66616499999999</v>
+        <v>80.35453112499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1817133980104896</v>
+        <v>0.1886680309496229</v>
       </c>
       <c r="T82">
-        <v>2.649205102699127</v>
+        <v>2.784763843334316</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.658013550356166</v>
+        <v>3.612852889240659</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07929330088042834</v>
+        <v>0.07933392215875876</v>
       </c>
       <c r="C83">
-        <v>97.87656861702237</v>
+        <v>91.89243682755074</v>
       </c>
       <c r="D83">
-        <v>433.6865686170224</v>
+        <v>433.5124368275507</v>
       </c>
       <c r="E83">
-        <v>191.11</v>
+        <v>196.92</v>
       </c>
       <c r="F83">
-        <v>470.61</v>
+        <v>476.42</v>
       </c>
       <c r="G83">
         <v>134.8</v>
@@ -8093,28 +8093,28 @@
         <v>104.225</v>
       </c>
       <c r="M83">
-        <v>28.848393</v>
+        <v>29.204546</v>
       </c>
       <c r="N83">
-        <v>75.37660699999999</v>
+        <v>75.020454</v>
       </c>
       <c r="O83">
-        <v>9.422075874999999</v>
+        <v>9.37755675</v>
       </c>
       <c r="P83">
-        <v>65.95453112499999</v>
+        <v>65.64289725</v>
       </c>
       <c r="Q83">
-        <v>80.35453112499999</v>
+        <v>80.04289725000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1886680309496229</v>
+        <v>0.1963954008819931</v>
       </c>
       <c r="T83">
-        <v>2.784763843334316</v>
+        <v>2.935384666262304</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.612852889240659</v>
+        <v>3.568793707664554</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07933392215875876</v>
+        <v>0.07937454343708916</v>
       </c>
       <c r="C84">
-        <v>91.89243682755074</v>
+        <v>85.90844481510931</v>
       </c>
       <c r="D84">
-        <v>433.5124368275507</v>
+        <v>433.3384448151093</v>
       </c>
       <c r="E84">
-        <v>196.92</v>
+        <v>202.73</v>
       </c>
       <c r="F84">
-        <v>476.42</v>
+        <v>482.23</v>
       </c>
       <c r="G84">
         <v>134.8</v>
@@ -8175,28 +8175,28 @@
         <v>104.225</v>
       </c>
       <c r="M84">
-        <v>29.204546</v>
+        <v>29.560699</v>
       </c>
       <c r="N84">
-        <v>75.020454</v>
+        <v>74.66430099999999</v>
       </c>
       <c r="O84">
-        <v>9.37755675</v>
+        <v>9.333037624999999</v>
       </c>
       <c r="P84">
-        <v>65.64289725</v>
+        <v>65.33126337499999</v>
       </c>
       <c r="Q84">
-        <v>80.04289725000001</v>
+        <v>79.731263375</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1963954008819931</v>
+        <v>0.2050318731593481</v>
       </c>
       <c r="T84">
-        <v>2.935384666262304</v>
+        <v>3.10372558600535</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.568793707664554</v>
+        <v>3.525796193114378</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07937454343708916</v>
+        <v>0.0814731647154196</v>
       </c>
       <c r="C85">
-        <v>85.90844481510931</v>
+        <v>71.29561381320667</v>
       </c>
       <c r="D85">
-        <v>433.3384448151093</v>
+        <v>424.5356138132067</v>
       </c>
       <c r="E85">
-        <v>202.73</v>
+        <v>208.54</v>
       </c>
       <c r="F85">
-        <v>482.23</v>
+        <v>488.04</v>
       </c>
       <c r="G85">
         <v>134.8</v>
@@ -8257,45 +8257,45 @@
         <v>104.225</v>
       </c>
       <c r="M85">
-        <v>29.560699</v>
+        <v>31.283364</v>
       </c>
       <c r="N85">
-        <v>74.66430099999999</v>
+        <v>72.94163599999999</v>
       </c>
       <c r="O85">
-        <v>9.333037624999999</v>
+        <v>9.117704499999999</v>
       </c>
       <c r="P85">
-        <v>65.33126337499999</v>
+        <v>63.82393149999999</v>
       </c>
       <c r="Q85">
-        <v>79.731263375</v>
+        <v>78.22393149999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2050318731593481</v>
+        <v>0.2147479044713726</v>
       </c>
       <c r="T85">
-        <v>3.10372558600535</v>
+        <v>3.293109120716277</v>
       </c>
       <c r="U85">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V85">
         <v>0.125</v>
       </c>
       <c r="W85">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.525796193114378</v>
+        <v>3.331642978037783</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0814731647154196</v>
+        <v>0.08153828599375001</v>
       </c>
       <c r="C86">
-        <v>71.29561381320673</v>
+        <v>65.21817499466209</v>
       </c>
       <c r="D86">
-        <v>424.5356138132067</v>
+        <v>424.268174994662</v>
       </c>
       <c r="E86">
-        <v>208.54</v>
+        <v>214.35</v>
       </c>
       <c r="F86">
-        <v>488.04</v>
+        <v>493.85</v>
       </c>
       <c r="G86">
         <v>134.8</v>
@@ -8339,28 +8339,28 @@
         <v>104.225</v>
       </c>
       <c r="M86">
-        <v>31.283364</v>
+        <v>31.655785</v>
       </c>
       <c r="N86">
-        <v>72.94163599999999</v>
+        <v>72.56921499999999</v>
       </c>
       <c r="O86">
-        <v>9.117704499999999</v>
+        <v>9.071151874999998</v>
       </c>
       <c r="P86">
-        <v>63.82393149999999</v>
+        <v>63.49806312499999</v>
       </c>
       <c r="Q86">
-        <v>78.22393149999999</v>
+        <v>77.89806312499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2147479044713725</v>
+        <v>0.2257594066250001</v>
       </c>
       <c r="T86">
-        <v>3.293109120716275</v>
+        <v>3.507743793388658</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.331642978037784</v>
+        <v>3.292447178296162</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08153828599375001</v>
+        <v>0.08160340727208044</v>
       </c>
       <c r="C87">
-        <v>65.21817499466209</v>
+        <v>59.14107291344169</v>
       </c>
       <c r="D87">
-        <v>424.268174994662</v>
+        <v>424.0010729134416</v>
       </c>
       <c r="E87">
-        <v>214.35</v>
+        <v>220.16</v>
       </c>
       <c r="F87">
-        <v>493.85</v>
+        <v>499.66</v>
       </c>
       <c r="G87">
         <v>134.8</v>
@@ -8421,28 +8421,28 @@
         <v>104.225</v>
       </c>
       <c r="M87">
-        <v>31.655785</v>
+        <v>32.028206</v>
       </c>
       <c r="N87">
-        <v>72.56921499999999</v>
+        <v>72.196794</v>
       </c>
       <c r="O87">
-        <v>9.071151874999998</v>
+        <v>9.02459925</v>
       </c>
       <c r="P87">
-        <v>63.49806312499999</v>
+        <v>63.17219475</v>
       </c>
       <c r="Q87">
-        <v>77.89806312499999</v>
+        <v>77.57219474999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2257594066250001</v>
+        <v>0.2383439805148602</v>
       </c>
       <c r="T87">
-        <v>3.507743793388658</v>
+        <v>3.753040562157096</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.292447178296162</v>
+        <v>3.254162908781091</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08160340727208044</v>
+        <v>0.08166852855041086</v>
       </c>
       <c r="C88">
-        <v>59.14107291344169</v>
+        <v>53.06430693395731</v>
       </c>
       <c r="D88">
-        <v>424.0010729134416</v>
+        <v>423.7343069339573</v>
       </c>
       <c r="E88">
-        <v>220.16</v>
+        <v>225.97</v>
       </c>
       <c r="F88">
-        <v>499.66</v>
+        <v>505.47</v>
       </c>
       <c r="G88">
         <v>134.8</v>
@@ -8503,28 +8503,28 @@
         <v>104.225</v>
       </c>
       <c r="M88">
-        <v>32.028206</v>
+        <v>32.400627</v>
       </c>
       <c r="N88">
-        <v>72.196794</v>
+        <v>71.82437299999999</v>
       </c>
       <c r="O88">
-        <v>9.02459925</v>
+        <v>8.978046624999999</v>
       </c>
       <c r="P88">
-        <v>63.17219475</v>
+        <v>62.846326375</v>
       </c>
       <c r="Q88">
-        <v>77.57219474999999</v>
+        <v>77.246326375</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2383439805148602</v>
+        <v>0.2528646426954681</v>
       </c>
       <c r="T88">
-        <v>3.753040562157096</v>
+        <v>4.036075295351447</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.254162908781091</v>
+        <v>3.216758737415791</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08166852855041086</v>
+        <v>0.08173364982874128</v>
       </c>
       <c r="C89">
-        <v>53.06430693395731</v>
+        <v>46.98787642221879</v>
       </c>
       <c r="D89">
-        <v>423.7343069339573</v>
+        <v>423.4678764222188</v>
       </c>
       <c r="E89">
-        <v>225.97</v>
+        <v>231.78</v>
       </c>
       <c r="F89">
-        <v>505.47</v>
+        <v>511.28</v>
       </c>
       <c r="G89">
         <v>134.8</v>
@@ -8585,28 +8585,28 @@
         <v>104.225</v>
       </c>
       <c r="M89">
-        <v>32.400627</v>
+        <v>32.773048</v>
       </c>
       <c r="N89">
-        <v>71.82437299999999</v>
+        <v>71.45195199999999</v>
       </c>
       <c r="O89">
-        <v>8.978046624999999</v>
+        <v>8.931493999999999</v>
       </c>
       <c r="P89">
-        <v>62.846326375</v>
+        <v>62.52045799999999</v>
       </c>
       <c r="Q89">
-        <v>77.246326375</v>
+        <v>76.920458</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2528646426954681</v>
+        <v>0.2698054152395106</v>
       </c>
       <c r="T89">
-        <v>4.036075295351447</v>
+        <v>4.36628248407819</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.216758737415791</v>
+        <v>3.180204660854248</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08173364982874128</v>
+        <v>0.08179877110707169</v>
       </c>
       <c r="C90">
-        <v>46.98787642221879</v>
+        <v>40.91178074583001</v>
       </c>
       <c r="D90">
-        <v>423.4678764222188</v>
+        <v>423.2017807458301</v>
       </c>
       <c r="E90">
-        <v>231.78</v>
+        <v>237.59</v>
       </c>
       <c r="F90">
-        <v>511.28</v>
+        <v>517.09</v>
       </c>
       <c r="G90">
         <v>134.8</v>
@@ -8667,28 +8667,28 @@
         <v>104.225</v>
       </c>
       <c r="M90">
-        <v>32.773048</v>
+        <v>33.14546900000001</v>
       </c>
       <c r="N90">
-        <v>71.45195199999999</v>
+        <v>71.07953099999999</v>
       </c>
       <c r="O90">
-        <v>8.931493999999999</v>
+        <v>8.884941374999999</v>
       </c>
       <c r="P90">
-        <v>62.52045799999999</v>
+        <v>62.19458962499999</v>
       </c>
       <c r="Q90">
-        <v>76.920458</v>
+        <v>76.594589625</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2698054152395106</v>
+        <v>0.2898263282461063</v>
       </c>
       <c r="T90">
-        <v>4.36628248407819</v>
+        <v>4.756527343482523</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.180204660854248</v>
+        <v>3.144472024215436</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08179877110707169</v>
+        <v>0.08186389238540212</v>
       </c>
       <c r="C91">
-        <v>40.91178074583001</v>
+        <v>34.83601927398308</v>
       </c>
       <c r="D91">
-        <v>423.2017807458301</v>
+        <v>422.936019273983</v>
       </c>
       <c r="E91">
-        <v>237.59</v>
+        <v>243.4</v>
       </c>
       <c r="F91">
-        <v>517.09</v>
+        <v>522.9</v>
       </c>
       <c r="G91">
         <v>134.8</v>
@@ -8749,28 +8749,28 @@
         <v>104.225</v>
       </c>
       <c r="M91">
-        <v>33.14546900000001</v>
+        <v>33.51789</v>
       </c>
       <c r="N91">
-        <v>71.07953099999999</v>
+        <v>70.70711</v>
       </c>
       <c r="O91">
-        <v>8.884941374999999</v>
+        <v>8.83838875</v>
       </c>
       <c r="P91">
-        <v>62.19458962499999</v>
+        <v>61.86872125</v>
       </c>
       <c r="Q91">
-        <v>76.594589625</v>
+        <v>76.26872125</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2898263282461063</v>
+        <v>0.3138514238540211</v>
       </c>
       <c r="T91">
-        <v>4.756527343482523</v>
+        <v>5.224821174767722</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.144472024215436</v>
+        <v>3.109533446168598</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08186389238540212</v>
+        <v>0.08192901366373254</v>
       </c>
       <c r="C92">
-        <v>34.83601927398308</v>
+        <v>28.76059137745347</v>
       </c>
       <c r="D92">
-        <v>422.936019273983</v>
+        <v>422.6705913774535</v>
       </c>
       <c r="E92">
-        <v>243.4</v>
+        <v>249.21</v>
       </c>
       <c r="F92">
-        <v>522.9</v>
+        <v>528.71</v>
       </c>
       <c r="G92">
         <v>134.8</v>
@@ -8831,28 +8831,28 @@
         <v>104.225</v>
       </c>
       <c r="M92">
-        <v>33.51789</v>
+        <v>33.890311</v>
       </c>
       <c r="N92">
-        <v>70.70711</v>
+        <v>70.334689</v>
       </c>
       <c r="O92">
-        <v>8.83838875</v>
+        <v>8.791836125</v>
       </c>
       <c r="P92">
-        <v>61.86872125</v>
+        <v>61.54285287499999</v>
       </c>
       <c r="Q92">
-        <v>76.26872125</v>
+        <v>75.942852875</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3138514238540211</v>
+        <v>0.3432154295970282</v>
       </c>
       <c r="T92">
-        <v>5.224821174767722</v>
+        <v>5.797180301894078</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.109533446168598</v>
+        <v>3.075362748957954</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08192901366373254</v>
+        <v>0.08199413494206295</v>
       </c>
       <c r="C93">
-        <v>28.76059137745347</v>
+        <v>22.6854964285958</v>
       </c>
       <c r="D93">
-        <v>422.6705913774535</v>
+        <v>422.4054964285958</v>
       </c>
       <c r="E93">
-        <v>249.21</v>
+        <v>255.02</v>
       </c>
       <c r="F93">
-        <v>528.71</v>
+        <v>534.52</v>
       </c>
       <c r="G93">
         <v>134.8</v>
@@ -8913,28 +8913,28 @@
         <v>104.225</v>
       </c>
       <c r="M93">
-        <v>33.890311</v>
+        <v>34.262732</v>
       </c>
       <c r="N93">
-        <v>70.334689</v>
+        <v>69.96226799999999</v>
       </c>
       <c r="O93">
-        <v>8.791836125</v>
+        <v>8.745283499999999</v>
       </c>
       <c r="P93">
-        <v>61.54285287499999</v>
+        <v>61.2169845</v>
       </c>
       <c r="Q93">
-        <v>75.942852875</v>
+        <v>75.6169845</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3432154295970282</v>
+        <v>0.3799204367757871</v>
       </c>
       <c r="T93">
-        <v>5.797180301894078</v>
+        <v>6.512629210802023</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.075362748957954</v>
+        <v>3.04193489299102</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08199413494206295</v>
+        <v>0.08205925622039338</v>
       </c>
       <c r="C94">
-        <v>22.6854964285958</v>
+        <v>16.61073380133746</v>
       </c>
       <c r="D94">
-        <v>422.4054964285958</v>
+        <v>422.1407338013375</v>
       </c>
       <c r="E94">
-        <v>255.02</v>
+        <v>260.83</v>
       </c>
       <c r="F94">
-        <v>534.52</v>
+        <v>540.33</v>
       </c>
       <c r="G94">
         <v>134.8</v>
@@ -8995,28 +8995,28 @@
         <v>104.225</v>
       </c>
       <c r="M94">
-        <v>34.262732</v>
+        <v>34.635153</v>
       </c>
       <c r="N94">
-        <v>69.96226799999999</v>
+        <v>69.58984699999999</v>
       </c>
       <c r="O94">
-        <v>8.745283499999999</v>
+        <v>8.698730874999999</v>
       </c>
       <c r="P94">
-        <v>61.2169845</v>
+        <v>60.891116125</v>
       </c>
       <c r="Q94">
-        <v>75.6169845</v>
+        <v>75.291116125</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3799204367757871</v>
+        <v>0.4271125888627627</v>
       </c>
       <c r="T94">
-        <v>6.512629210802023</v>
+        <v>7.432492093683666</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.04193489299102</v>
+        <v>3.00922591564703</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08205925622039338</v>
+        <v>0.0885398774987238</v>
       </c>
       <c r="C95">
-        <v>16.61073380133746</v>
+        <v>-13.98487900439375</v>
       </c>
       <c r="D95">
-        <v>422.1407338013375</v>
+        <v>397.3551209956062</v>
       </c>
       <c r="E95">
-        <v>260.83</v>
+        <v>266.64</v>
       </c>
       <c r="F95">
-        <v>540.33</v>
+        <v>546.14</v>
       </c>
       <c r="G95">
         <v>134.8</v>
@@ -9077,45 +9077,45 @@
         <v>104.225</v>
       </c>
       <c r="M95">
-        <v>34.635153</v>
+        <v>39.267466</v>
       </c>
       <c r="N95">
-        <v>69.58984699999999</v>
+        <v>64.957534</v>
       </c>
       <c r="O95">
-        <v>8.698730874999999</v>
+        <v>8.119691749999999</v>
       </c>
       <c r="P95">
-        <v>60.891116125</v>
+        <v>56.83784224999999</v>
       </c>
       <c r="Q95">
-        <v>75.291116125</v>
+        <v>71.23784225</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4271125888627627</v>
+        <v>0.4900354583120635</v>
       </c>
       <c r="T95">
-        <v>7.432492093683666</v>
+        <v>8.658975937525856</v>
       </c>
       <c r="U95">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V95">
         <v>0.125</v>
       </c>
       <c r="W95">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.00922591564703</v>
+        <v>2.654232896006073</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0885398774987238</v>
+        <v>0.08867324877705421</v>
       </c>
       <c r="C96">
-        <v>-13.98487900439375</v>
+        <v>-20.27443842716696</v>
       </c>
       <c r="D96">
-        <v>397.3551209956062</v>
+        <v>396.8755615728331</v>
       </c>
       <c r="E96">
-        <v>266.64</v>
+        <v>272.45</v>
       </c>
       <c r="F96">
-        <v>546.14</v>
+        <v>551.95</v>
       </c>
       <c r="G96">
         <v>134.8</v>
@@ -9159,28 +9159,28 @@
         <v>104.225</v>
       </c>
       <c r="M96">
-        <v>39.267466</v>
+        <v>39.685205</v>
       </c>
       <c r="N96">
-        <v>64.957534</v>
+        <v>64.539795</v>
       </c>
       <c r="O96">
-        <v>8.119691749999999</v>
+        <v>8.067474375</v>
       </c>
       <c r="P96">
-        <v>56.83784224999999</v>
+        <v>56.47232062499999</v>
       </c>
       <c r="Q96">
-        <v>71.23784225</v>
+        <v>70.872320625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4900354583120635</v>
+        <v>0.5781274755410849</v>
       </c>
       <c r="T96">
-        <v>8.658975937525856</v>
+        <v>10.37605331890493</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.654232896006073</v>
+        <v>2.626293602363903</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08867324877705421</v>
+        <v>0.08880662005538463</v>
       </c>
       <c r="C97">
-        <v>-20.27443842716696</v>
+        <v>-26.5628417051829</v>
       </c>
       <c r="D97">
-        <v>396.8755615728331</v>
+        <v>396.3971582948171</v>
       </c>
       <c r="E97">
-        <v>272.45</v>
+        <v>278.26</v>
       </c>
       <c r="F97">
-        <v>551.95</v>
+        <v>557.76</v>
       </c>
       <c r="G97">
         <v>134.8</v>
@@ -9241,28 +9241,28 @@
         <v>104.225</v>
       </c>
       <c r="M97">
-        <v>39.685205</v>
+        <v>40.102944</v>
       </c>
       <c r="N97">
-        <v>64.539795</v>
+        <v>64.12205599999999</v>
       </c>
       <c r="O97">
-        <v>8.067474375</v>
+        <v>8.015256999999998</v>
       </c>
       <c r="P97">
-        <v>56.47232062499999</v>
+        <v>56.10679899999999</v>
       </c>
       <c r="Q97">
-        <v>70.872320625</v>
+        <v>70.50679899999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5781274755410849</v>
+        <v>0.7102655013846169</v>
       </c>
       <c r="T97">
-        <v>10.37605331890493</v>
+        <v>12.95166939097353</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.626293602363903</v>
+        <v>2.598936377339279</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08880662005538464</v>
+        <v>0.08893999133371507</v>
       </c>
       <c r="C98">
-        <v>-26.56284170518302</v>
+        <v>-32.85009301434172</v>
       </c>
       <c r="D98">
-        <v>396.397158294817</v>
+        <v>395.9199069856582</v>
       </c>
       <c r="E98">
-        <v>278.26</v>
+        <v>284.0699999999999</v>
       </c>
       <c r="F98">
-        <v>557.76</v>
+        <v>563.5699999999999</v>
       </c>
       <c r="G98">
         <v>134.8</v>
@@ -9323,28 +9323,28 @@
         <v>104.225</v>
       </c>
       <c r="M98">
-        <v>40.102944</v>
+        <v>40.520683</v>
       </c>
       <c r="N98">
-        <v>64.12205599999999</v>
+        <v>63.704317</v>
       </c>
       <c r="O98">
-        <v>8.015256999999998</v>
+        <v>7.963039625</v>
       </c>
       <c r="P98">
-        <v>56.10679899999999</v>
+        <v>55.741277375</v>
       </c>
       <c r="Q98">
-        <v>70.50679899999999</v>
+        <v>70.141277375</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7102655013846152</v>
+        <v>0.9304955444571676</v>
       </c>
       <c r="T98">
-        <v>12.9516693909735</v>
+        <v>17.24436284442115</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.598936377339279</v>
+        <v>2.572143218810009</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08893999133371507</v>
+        <v>0.08907336261204549</v>
       </c>
       <c r="C99">
-        <v>-32.85009301434172</v>
+        <v>-39.13619651045644</v>
       </c>
       <c r="D99">
-        <v>395.9199069856582</v>
+        <v>395.4438034895435</v>
       </c>
       <c r="E99">
-        <v>284.0699999999999</v>
+        <v>289.88</v>
       </c>
       <c r="F99">
-        <v>563.5699999999999</v>
+        <v>569.38</v>
       </c>
       <c r="G99">
         <v>134.8</v>
@@ -9405,28 +9405,28 @@
         <v>104.225</v>
       </c>
       <c r="M99">
-        <v>40.520683</v>
+        <v>40.938422</v>
       </c>
       <c r="N99">
-        <v>63.704317</v>
+        <v>63.28657799999999</v>
       </c>
       <c r="O99">
-        <v>7.963039625</v>
+        <v>7.910822249999999</v>
       </c>
       <c r="P99">
-        <v>55.741277375</v>
+        <v>55.37575575</v>
       </c>
       <c r="Q99">
-        <v>70.141277375</v>
+        <v>69.77575575</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9304955444571676</v>
+        <v>1.370955630602272</v>
       </c>
       <c r="T99">
-        <v>17.24436284442115</v>
+        <v>25.82974975131646</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.572143218810009</v>
+        <v>2.545896859434396</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08907336261204549</v>
+        <v>0.08920673389037589</v>
       </c>
       <c r="C100">
-        <v>-39.13619651045644</v>
+        <v>-45.42115632937441</v>
       </c>
       <c r="D100">
-        <v>395.4438034895435</v>
+        <v>394.9688436706255</v>
       </c>
       <c r="E100">
-        <v>289.88</v>
+        <v>295.6899999999999</v>
       </c>
       <c r="F100">
-        <v>569.38</v>
+        <v>575.1899999999999</v>
       </c>
       <c r="G100">
         <v>134.8</v>
@@ -9487,28 +9487,28 @@
         <v>104.225</v>
       </c>
       <c r="M100">
-        <v>40.938422</v>
+        <v>41.356161</v>
       </c>
       <c r="N100">
-        <v>63.28657799999999</v>
+        <v>62.86883899999999</v>
       </c>
       <c r="O100">
-        <v>7.910822249999999</v>
+        <v>7.858604874999999</v>
       </c>
       <c r="P100">
-        <v>55.37575575</v>
+        <v>55.010234125</v>
       </c>
       <c r="Q100">
-        <v>69.77575575</v>
+        <v>69.410234125</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.370955630602272</v>
+        <v>2.692335889037587</v>
       </c>
       <c r="T100">
-        <v>25.82974975131646</v>
+        <v>51.5859104720024</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.545896859434396</v>
+        <v>2.52018072954112</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08920673389037589</v>
-      </c>
-      <c r="C101">
-        <v>-45.42115632937441</v>
-      </c>
-      <c r="D101">
-        <v>394.9688436706255</v>
-      </c>
-      <c r="E101">
-        <v>295.6899999999999</v>
-      </c>
-      <c r="F101">
-        <v>575.1899999999999</v>
-      </c>
-      <c r="G101">
-        <v>134.8</v>
-      </c>
-      <c r="H101">
-        <v>301.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>118.625</v>
-      </c>
-      <c r="K101">
-        <v>14.4</v>
-      </c>
-      <c r="L101">
-        <v>104.225</v>
-      </c>
-      <c r="M101">
-        <v>41.356161</v>
-      </c>
-      <c r="N101">
-        <v>62.86883899999999</v>
-      </c>
-      <c r="O101">
-        <v>7.858604874999999</v>
-      </c>
-      <c r="P101">
-        <v>55.010234125</v>
-      </c>
-      <c r="Q101">
-        <v>69.410234125</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.692335889037587</v>
-      </c>
-      <c r="T101">
-        <v>51.5859104720024</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.125</v>
-      </c>
-      <c r="W101">
-        <v>0.06291250000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.52018072954112</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
